--- a/株式会社ワクトリ御中_LINEOA施策提案【SIM】ver1.0.xlsx
+++ b/株式会社ワクトリ御中_LINEOA施策提案【SIM】ver1.0.xlsx
@@ -19,7 +19,7 @@
     <sheet name="SIM②_比較" sheetId="4" r:id="rId4"/>
     <sheet name="SIM考え方" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr fullCalcOnLoad="1" calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -6286,7 +6286,7 @@
         <v>164</v>
       </c>
       <c r="D8" s="33">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="G8" s="121" t="s">
         <v>66</v>
@@ -6456,31 +6456,24 @@
       <c r="C14" s="99"/>
       <c r="D14" s="42">
         <f>+H8</f>
-        <v>85887</v>
       </c>
       <c r="E14" s="43">
         <f>+D14</f>
-        <v>85887</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" ref="F14:J14" si="0">+E14</f>
-        <v>85887</v>
       </c>
       <c r="G14" s="43">
         <f t="shared" si="0"/>
-        <v>85887</v>
       </c>
       <c r="H14" s="43">
         <f t="shared" si="0"/>
-        <v>85887</v>
       </c>
       <c r="I14" s="43">
         <f t="shared" si="0"/>
-        <v>85887</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="0"/>
-        <v>85887</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
@@ -6493,31 +6486,24 @@
       <c r="C15" s="99"/>
       <c r="D15" s="42">
         <f t="shared" ref="D15" si="1">+H9</f>
-        <v>0</v>
       </c>
       <c r="E15" s="43">
         <f t="shared" ref="E15:J16" si="2">+D15</f>
-        <v>0</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="H15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="I15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
@@ -6542,31 +6528,24 @@
       <c r="C16" s="99"/>
       <c r="D16" s="42">
         <f>H10</f>
-        <v>400</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -6747,7 +6726,6 @@
       </c>
       <c r="Y19" s="34">
         <f>+U19*2.5</f>
-        <v>37500000</v>
       </c>
       <c r="Z19" s="35">
         <v>2.5</v>
@@ -6888,27 +6866,21 @@
       </c>
       <c r="E23" s="46">
         <f>IF(E18=FALSE,0,E15*$P$18*0.08*0.08+(E14-E15)*$P$19*0.12*0.12)</f>
-        <v>680.22504000000004</v>
       </c>
       <c r="F23" s="46">
         <f>IF(F18=FALSE,0,F15*$P$18*0.08*0.08+(F14-F15)*$P$19*0.12*0.12)</f>
-        <v>680.22504000000004</v>
       </c>
       <c r="G23" s="63">
         <f t="shared" ref="G23:J23" si="3">F23*1.01</f>
-        <v>687.02729040000008</v>
       </c>
       <c r="H23" s="63">
         <f t="shared" si="3"/>
-        <v>693.89756330400007</v>
       </c>
       <c r="I23" s="63">
         <f t="shared" si="3"/>
-        <v>700.83653893704013</v>
       </c>
       <c r="J23" s="63">
         <f t="shared" si="3"/>
-        <v>707.84490432641053</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
@@ -6941,27 +6913,21 @@
       </c>
       <c r="E24" s="46">
         <f t="shared" ref="E24:J24" si="4">IF(E19=FALSE,0,$H$10*0.8*0.45)</f>
-        <v>0</v>
       </c>
       <c r="F24" s="63">
         <f t="shared" si="4"/>
-        <v>0</v>
       </c>
       <c r="G24" s="63">
         <f t="shared" si="4"/>
-        <v>0</v>
       </c>
       <c r="H24" s="63">
         <f t="shared" si="4"/>
-        <v>0</v>
       </c>
       <c r="I24" s="63">
         <f t="shared" si="4"/>
-        <v>0</v>
       </c>
       <c r="J24" s="63">
         <f t="shared" si="4"/>
-        <v>0</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
@@ -6994,27 +6960,21 @@
       </c>
       <c r="E25" s="46">
         <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
-        <v>0</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" ref="F25:J25" si="5">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
-        <v>0</v>
       </c>
       <c r="G25" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
       </c>
       <c r="I25" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
       </c>
       <c r="J25" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="7"/>
@@ -7042,27 +7002,21 @@
       </c>
       <c r="E26" s="46">
         <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
-        <v>1109.66004</v>
       </c>
       <c r="F26" s="46">
         <f t="shared" ref="F26:J26" si="6">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
-        <v>1109.66004</v>
       </c>
       <c r="G26" s="46">
         <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
-        <v>1116.4622904</v>
       </c>
       <c r="H26" s="46">
         <f t="shared" si="6"/>
-        <v>1123.3325633040001</v>
       </c>
       <c r="I26" s="46">
         <f t="shared" si="6"/>
-        <v>1130.2715389370401</v>
       </c>
       <c r="J26" s="46">
         <f t="shared" si="6"/>
-        <v>1137.2799043264106</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
@@ -7088,30 +7042,25 @@
       <c r="B27" s="145"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
-        <v>0.4</v>
+        <v>0.341</v>
       </c>
       <c r="E27" s="47">
-        <v>0.4</v>
+        <v>0.341</v>
       </c>
       <c r="F27" s="47">
         <f>ROUND(E27*1.02,3)</f>
-        <v>0.40799999999999997</v>
       </c>
       <c r="G27" s="47">
         <f>ROUND(F27*1.02,3)</f>
-        <v>0.41599999999999998</v>
       </c>
       <c r="H27" s="47">
         <f>ROUND(G27*1.02,3)</f>
-        <v>0.42399999999999999</v>
       </c>
       <c r="I27" s="47">
         <f>ROUND(H27*1.02,3)</f>
-        <v>0.432</v>
       </c>
       <c r="J27" s="47">
         <f>ROUND(I27*1.02,3)</f>
-        <v>0.441</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
@@ -7144,27 +7093,21 @@
       </c>
       <c r="E28" s="49">
         <f>+D28+E26</f>
-        <v>81013.660040000002</v>
       </c>
       <c r="F28" s="49">
         <f t="shared" ref="F28:J28" si="7">+E28+F26</f>
-        <v>82123.320080000005</v>
       </c>
       <c r="G28" s="49">
         <f t="shared" si="7"/>
-        <v>83239.782370400004</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="7"/>
-        <v>84363.114933703997</v>
       </c>
       <c r="I28" s="49">
         <f t="shared" si="7"/>
-        <v>85493.386472641039</v>
       </c>
       <c r="J28" s="49">
         <f t="shared" si="7"/>
-        <v>86630.666376967449</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
@@ -7194,31 +7137,24 @@
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
-        <v>47942.400000000001</v>
       </c>
       <c r="E29" s="50">
         <f>+E28*(1-E27)</f>
-        <v>48608.196023999997</v>
       </c>
       <c r="F29" s="50">
         <f t="shared" ref="F29:J29" si="8">+F28*(1-F27)</f>
-        <v>48617.005487360009</v>
       </c>
       <c r="G29" s="50">
         <f t="shared" si="8"/>
-        <v>48612.032904313608</v>
       </c>
       <c r="H29" s="50">
         <f t="shared" si="8"/>
-        <v>48593.154201813508</v>
       </c>
       <c r="I29" s="50">
         <f t="shared" si="8"/>
-        <v>48560.243516460112</v>
       </c>
       <c r="J29" s="50">
         <f t="shared" si="8"/>
-        <v>48426.542504724799</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -7281,31 +7217,24 @@
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
-        <v>5503.7875199999999</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>22204.185057206396</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>22208.209213021673</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>22205.937741064146</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>17757.851171892049</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>17745.824312099347</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>17696.964699939443</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -7355,7 +7284,6 @@
       </c>
       <c r="Q32" s="73">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
-        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
@@ -7373,27 +7301,21 @@
       </c>
       <c r="E33" s="63">
         <f t="shared" ref="E33:J33" si="9">+(E26-E24)*E32*$P$26*$P$27*$P$36</f>
-        <v>706.72417008534012</v>
       </c>
       <c r="F33" s="63">
         <f t="shared" si="9"/>
-        <v>706.72417008534012</v>
       </c>
       <c r="G33" s="63">
         <f t="shared" si="9"/>
-        <v>711.05641112796854</v>
       </c>
       <c r="H33" s="63">
         <f t="shared" si="9"/>
-        <v>715.43197458102338</v>
       </c>
       <c r="I33" s="63">
         <f t="shared" si="9"/>
-        <v>719.85129366860861</v>
       </c>
       <c r="J33" s="63">
         <f t="shared" si="9"/>
-        <v>724.31480594706977</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -7405,7 +7327,6 @@
       </c>
       <c r="Q33" s="73">
         <f t="shared" ref="Q33:Q35" si="10">+IF(P33=TRUE,1.1,0.95)</f>
-        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
@@ -7416,31 +7337,24 @@
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
-        <v>191769.60000000001</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E26*E32</f>
-        <v>199981.08429600002</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F26*F32</f>
-        <v>200016.32214944003</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G26*G32</f>
-        <v>200030.44306925446</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H26*H32</f>
-        <v>161114.75626232324</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I26*I32</f>
-        <v>161044.13694735759</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J26*J32</f>
-        <v>160651.33553675146</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -7452,7 +7366,6 @@
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="10"/>
-        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
@@ -7463,31 +7376,24 @@
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
-        <v>5613.8632704000001</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
-        <v>46967.363915948066</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" ref="F35:J35" si="11">+F31+F33+1.05*(F31+F33)</f>
-        <v>46975.613435369378</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="11"/>
-        <v>46979.838011993837</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="11"/>
-        <v>37870.230450269803</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="11"/>
-        <v>37854.634991824307</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="11"/>
-        <v>37763.622987067356</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -7499,48 +7405,39 @@
       </c>
       <c r="Q35" s="73">
         <f t="shared" si="10"/>
-        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="6" t="str">
+      <c r="B36" s="6">
         <f>+C8</f>
-        <v>応募</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="11">
         <v>0</v>
       </c>
       <c r="E36" s="111">
-        <f>ROUND(E35*0.003,0)</f>
-        <v>141</v>
+        <f>ROUND(E35*0.004,0)</f>
       </c>
       <c r="F36" s="111">
-        <f>ROUND(F35*0.0035,0)</f>
-        <v>164</v>
+        <f>ROUND(F35*0.0045,0)</f>
       </c>
       <c r="G36" s="111">
-        <f>ROUND(G35*0.004,0)</f>
-        <v>188</v>
+        <f>ROUND(G35*0.0055,0)</f>
       </c>
       <c r="H36" s="111">
-        <f>ROUND(H35*0.005,0)</f>
-        <v>189</v>
+        <f>ROUND(H35*0.0065,0)</f>
       </c>
       <c r="I36" s="111">
-        <f>ROUND(I35*0.0055,0)</f>
-        <v>208</v>
+        <f>ROUND(I35*0.0075,0)</f>
       </c>
       <c r="J36" s="111">
-        <f>ROUND(J35*0.006,0)</f>
-        <v>227</v>
+        <f>ROUND(J35*0.009,0)</f>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
-        <v>1117</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
@@ -7551,15 +7448,13 @@
       </c>
       <c r="P36" s="74">
         <f>1*(Q32*Q33*Q34*Q35)</f>
-        <v>1.4641000000000006</v>
       </c>
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="151"/>
-      <c r="B37" s="6" t="str">
+      <c r="B37" s="6">
         <f>+C9</f>
-        <v>-</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
@@ -7585,7 +7480,6 @@
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
-        <v>0</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
@@ -7596,9 +7490,8 @@
       <c r="A38" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6" t="str">
+      <c r="B38" s="6">
         <f>+C10</f>
-        <v>-</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="11">
@@ -7624,7 +7517,6 @@
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
-        <v>0</v>
       </c>
       <c r="L38" s="7"/>
       <c r="N38" s="69" t="s">
@@ -7636,9 +7528,8 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="151"/>
-      <c r="B39" s="6" t="str">
+      <c r="B39" s="6">
         <f>+C11</f>
-        <v>-</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="11">
@@ -7664,7 +7555,6 @@
       </c>
       <c r="K39" s="115">
         <f>SUM(E39:J39)</f>
-        <v>0</v>
       </c>
       <c r="L39" s="7"/>
       <c r="N39" s="69" t="s">
@@ -7682,35 +7572,27 @@
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="12">+SUM(D36:D39)</f>
-        <v>0</v>
       </c>
       <c r="E40" s="10">
         <f t="shared" si="12"/>
-        <v>141</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="12"/>
-        <v>164</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="12"/>
-        <v>188</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="12"/>
-        <v>189</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="12"/>
-        <v>208</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="12"/>
-        <v>227</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
-        <v>1117</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -7721,31 +7603,24 @@
       </c>
       <c r="D41" s="18">
         <f t="shared" ref="D41" si="13">+IFERROR(D40/D35,0)</f>
-        <v>0</v>
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
-        <v>3.0020846018169343E-3</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="14">+IFERROR(F40/F35,0)</f>
-        <v>3.4911731429678231E-3</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="14"/>
-        <v>4.0017166502788722E-3</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="14"/>
-        <v>4.9907274857540112E-3</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="14"/>
-        <v>5.4947036220247009E-3</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="14"/>
-        <v>6.0110757931710924E-3</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>118</v>
@@ -7783,27 +7658,21 @@
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
-        <v>509943.25288800005</v>
       </c>
       <c r="F44" s="31">
         <f t="shared" ref="F44:J44" si="15">+F75*F76</f>
-        <v>510048.96644832008</v>
       </c>
       <c r="G44" s="31">
         <f t="shared" si="15"/>
-        <v>510091.32920776337</v>
       </c>
       <c r="H44" s="31">
         <f t="shared" si="15"/>
-        <v>393344.26878696971</v>
       </c>
       <c r="I44" s="31">
         <f t="shared" si="15"/>
-        <v>393132.4108420728</v>
       </c>
       <c r="J44" s="31">
         <f t="shared" si="15"/>
-        <v>391954.00661025441</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
@@ -7815,35 +7684,27 @@
       <c r="B45" s="145"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
-        <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
-        <v>115000</v>
       </c>
       <c r="E45" s="27">
         <f t="shared" ref="E45:J45" si="16">SUM(E65:E68)+SUM(E71:E72)</f>
-        <v>45000</v>
       </c>
       <c r="F45" s="27">
         <f t="shared" si="16"/>
-        <v>45000</v>
       </c>
       <c r="G45" s="27">
         <f t="shared" si="16"/>
-        <v>45000</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="16"/>
-        <v>45000</v>
       </c>
       <c r="I45" s="27">
         <f t="shared" si="16"/>
-        <v>45000</v>
       </c>
       <c r="J45" s="27">
         <f t="shared" si="16"/>
-        <v>45000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
@@ -7862,27 +7723,21 @@
       </c>
       <c r="E46" s="28">
         <f t="shared" ref="E46:J46" si="17">+SUM(E65:E67)/(E28-D28)</f>
-        <v>27.035307137850914</v>
       </c>
       <c r="F46" s="28">
         <f t="shared" si="17"/>
-        <v>27.035307137850914</v>
       </c>
       <c r="G46" s="28">
         <f t="shared" si="17"/>
-        <v>26.870589591746796</v>
       </c>
       <c r="H46" s="28">
         <f t="shared" si="17"/>
-        <v>26.70624976076785</v>
       </c>
       <c r="I46" s="28">
         <f t="shared" si="17"/>
-        <v>26.542294454493064</v>
       </c>
       <c r="J46" s="28">
         <f t="shared" si="17"/>
-        <v>26.378730412693315</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
@@ -7898,27 +7753,21 @@
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="18">+E51/E35</f>
-        <v>23.823846168808632</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="18"/>
-        <v>25.780375771239726</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="18"/>
-        <v>27.822389018754514</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="18"/>
-        <v>31.537813596232304</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="18"/>
-        <v>33.552890184158187</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
-        <v>35.615068158869484</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
@@ -7934,27 +7783,21 @@
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="19">+SUM(E36:E39)/E35</f>
-        <v>3.0020846018169343E-3</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="19"/>
-        <v>3.4911731429678231E-3</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="19"/>
-        <v>4.0017166502788722E-3</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="19"/>
-        <v>4.9907274857540112E-3</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="19"/>
-        <v>5.4947036220247009E-3</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="19"/>
-        <v>6.0110757931710924E-3</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
@@ -7970,27 +7813,21 @@
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
-        <v>7935.7677509787245</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="20">+IFERROR(F51/SUM(F36:F39),0)</f>
-        <v>7384.4449173678049</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="20"/>
-        <v>6952.6134532327833</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="20"/>
-        <v>6319.2818454337012</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="20"/>
-        <v>6106.4058213561184</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="20"/>
-        <v>5924.9075181068474</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
@@ -8006,27 +7843,21 @@
       </c>
       <c r="E50" s="65">
         <f>+E36*$D$8+E38*$D$10</f>
-        <v>564000</v>
       </c>
       <c r="F50" s="65">
         <f t="shared" ref="F50:J50" si="21">+F36*$D$8+F38*$D$10</f>
-        <v>656000</v>
       </c>
       <c r="G50" s="65">
         <f t="shared" si="21"/>
-        <v>752000</v>
       </c>
       <c r="H50" s="65">
         <f t="shared" si="21"/>
-        <v>756000</v>
       </c>
       <c r="I50" s="65">
         <f t="shared" si="21"/>
-        <v>832000</v>
       </c>
       <c r="J50" s="65">
         <f t="shared" si="21"/>
-        <v>908000</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
@@ -8038,35 +7869,27 @@
       <c r="B51" s="155"/>
       <c r="C51" s="110">
         <f>+C45</f>
-        <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
-        <v>115000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
-        <v>1118943.2528880001</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="22">SUM(F45,F50)+F44</f>
-        <v>1211048.9664483201</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="22"/>
-        <v>1307091.3292077633</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="22"/>
-        <v>1194344.2687869696</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="22"/>
-        <v>1270132.4108420727</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
-        <v>1344954.0066102543</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -8096,31 +7919,24 @@
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
-        <v>485308.80000000005</v>
       </c>
       <c r="E54" s="28">
         <f t="shared" ref="E54:J54" si="23">+E75*E76</f>
-        <v>509943.25288800005</v>
       </c>
       <c r="F54" s="28">
         <f t="shared" si="23"/>
-        <v>510048.96644832008</v>
       </c>
       <c r="G54" s="28">
         <f t="shared" si="23"/>
-        <v>510091.32920776337</v>
       </c>
       <c r="H54" s="28">
         <f t="shared" si="23"/>
-        <v>393344.26878696971</v>
       </c>
       <c r="I54" s="28">
         <f t="shared" si="23"/>
-        <v>393132.4108420728</v>
       </c>
       <c r="J54" s="28">
         <f t="shared" si="23"/>
-        <v>391954.00661025441</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
@@ -8136,31 +7952,24 @@
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
-        <v>115000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
-        <v>824943.2528880001</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="24">SUM(F65:F72)+F54</f>
-        <v>825048.96644832008</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="24"/>
-        <v>825091.32920776331</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="24"/>
-        <v>708344.26878696971</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="24"/>
-        <v>708132.4108420728</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="24"/>
-        <v>706954.00661025441</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
@@ -8176,27 +7985,21 @@
       </c>
       <c r="E56" s="28">
         <f>+SUM(E65:E67)/(E28-D28)</f>
-        <v>27.035307137850914</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" ref="F56:J56" si="25">+SUM(F65:F67)/(F28-E28)</f>
-        <v>27.035307137850914</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="25"/>
-        <v>26.870589591746796</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="25"/>
-        <v>26.70624976076785</v>
       </c>
       <c r="I56" s="28">
         <f t="shared" si="25"/>
-        <v>26.542294454493064</v>
       </c>
       <c r="J56" s="28">
         <f t="shared" si="25"/>
-        <v>26.378730412693315</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
@@ -8212,27 +8015,21 @@
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
-        <v>17.564180403318002</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="26">+F61/F35</f>
-        <v>17.563346300595949</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="26"/>
-        <v>17.562668670699111</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="26"/>
-        <v>18.704514347150564</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="26"/>
-        <v>18.70662366695683</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="26"/>
-        <v>18.720502713745446</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
@@ -8248,27 +8045,21 @@
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="27">+SUM(E36:E39)/E35</f>
-        <v>3.0020846018169343E-3</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="27"/>
-        <v>3.4911731429678231E-3</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="27"/>
-        <v>4.0017166502788722E-3</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="27"/>
-        <v>4.9907274857540112E-3</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="27"/>
-        <v>5.4947036220247009E-3</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="27"/>
-        <v>6.0110757931710924E-3</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
@@ -8282,27 +8073,21 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
-        <v>5850.6613680000009</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="28">+IFERROR(F55/F40,0)</f>
-        <v>5030.7863807824397</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="28"/>
-        <v>4388.7836659987406</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="28"/>
-        <v>3747.853274005131</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="28"/>
-        <v>3404.4827444330422</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="28"/>
-        <v>3114.3348308821778</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
@@ -8331,31 +8116,24 @@
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
-        <v>115000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
-        <v>824943.2528880001</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="29">+SUM(F65:F72)+F54</f>
-        <v>825048.96644832008</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="29"/>
-        <v>825091.32920776331</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="29"/>
-        <v>708344.26878696971</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="29"/>
-        <v>708132.4108420728</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="29"/>
-        <v>706954.00661025441</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -8481,27 +8259,21 @@
       </c>
       <c r="E68" s="28">
         <f t="shared" ref="E68:J68" si="30">IF(E34&lt;5000,5000,15000)</f>
-        <v>15000</v>
       </c>
       <c r="F68" s="28">
         <f t="shared" si="30"/>
-        <v>15000</v>
       </c>
       <c r="G68" s="28">
         <f t="shared" si="30"/>
-        <v>15000</v>
       </c>
       <c r="H68" s="28">
         <f t="shared" si="30"/>
-        <v>15000</v>
       </c>
       <c r="I68" s="28">
         <f t="shared" si="30"/>
-        <v>15000</v>
       </c>
       <c r="J68" s="28">
         <f t="shared" si="30"/>
-        <v>15000</v>
       </c>
       <c r="N68" s="69" t="s">
         <v>190</v>
@@ -8655,31 +8427,24 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
-        <v>115000</v>
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="31">SUM(E65:E72)+E54</f>
-        <v>824943.2528880001</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="31"/>
-        <v>825048.96644832008</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="31"/>
-        <v>825091.32920776331</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="31"/>
-        <v>708344.26878696971</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="31"/>
-        <v>708132.4108420728</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="31"/>
-        <v>706954.00661025441</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8700,31 +8465,24 @@
       </c>
       <c r="D75" s="41">
         <f t="shared" ref="D75:J75" si="32">+IF(D34&lt;30001,0,D34-30000)</f>
-        <v>161769.60000000001</v>
       </c>
       <c r="E75" s="41">
         <f t="shared" si="32"/>
-        <v>169981.08429600002</v>
       </c>
       <c r="F75" s="41">
         <f t="shared" si="32"/>
-        <v>170016.32214944003</v>
       </c>
       <c r="G75" s="41">
         <f t="shared" si="32"/>
-        <v>170030.44306925446</v>
       </c>
       <c r="H75" s="41">
         <f t="shared" si="32"/>
-        <v>131114.75626232324</v>
       </c>
       <c r="I75" s="41">
         <f t="shared" si="32"/>
-        <v>131044.13694735759</v>
       </c>
       <c r="J75" s="41">
         <f t="shared" si="32"/>
-        <v>130651.33553675146</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8733,31 +8491,24 @@
       </c>
       <c r="D76" s="5">
         <f t="shared" ref="D76:J76" si="33">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="E76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
       <c r="F76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
       <c r="G76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
       <c r="H76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
       <c r="J76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -8847,17 +8598,14 @@
         <v>140</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="86" t="str">
+      <c r="C4" s="86">
         <f>+SIM②_月5投稿!D24</f>
-        <v>--</v>
       </c>
       <c r="D4" s="28">
         <f>+SIM②_月5投稿!G51</f>
-        <v>1307091.3292077633</v>
       </c>
       <c r="E4" s="28">
         <f>+SIM②_月5投稿!J51</f>
-        <v>1344954.0066102543</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -8866,17 +8614,14 @@
         <v>141</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="86" t="str">
+      <c r="C5" s="86">
         <f>+SIM②_月5投稿!D25</f>
-        <v>--</v>
       </c>
       <c r="D5" s="28">
         <f>+SIM②_月5投稿!G61</f>
-        <v>825091.32920776331</v>
       </c>
       <c r="E5" s="28">
         <f>+SIM②_月5投稿!J61</f>
-        <v>706954.00661025441</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -8887,15 +8632,12 @@
       <c r="B6" s="7"/>
       <c r="C6" s="117">
         <f>+SIM②_月5投稿!D28</f>
-        <v>79904</v>
       </c>
       <c r="D6" s="87">
         <f>+SIM②_月5投稿!G28</f>
-        <v>83239.782370400004</v>
       </c>
       <c r="E6" s="87">
         <f>+SIM②_月5投稿!J28</f>
-        <v>86630.666376967449</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -8906,15 +8648,12 @@
       <c r="B7" s="7"/>
       <c r="C7" s="88">
         <f>+SIM②_月5投稿!D27</f>
-        <v>0.4</v>
       </c>
       <c r="D7" s="89">
         <f>+SIM②_月5投稿!G27</f>
-        <v>0.41599999999999998</v>
       </c>
       <c r="E7" s="89">
         <f>+SIM②_月5投稿!J27</f>
-        <v>0.441</v>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -8925,15 +8664,12 @@
       <c r="B8" s="7"/>
       <c r="C8" s="117">
         <f>+SIM②_月5投稿!D29</f>
-        <v>47942.400000000001</v>
       </c>
       <c r="D8" s="10">
         <f>+SIM②_月5投稿!G29</f>
-        <v>48612.032904313608</v>
       </c>
       <c r="E8" s="10">
         <f>+SIM②_月5投稿!J29</f>
-        <v>48426.542504724799</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -8952,15 +8688,12 @@
       <c r="B10" s="7"/>
       <c r="C10" s="117">
         <f>+SIM②_月5投稿!D34</f>
-        <v>191769.60000000001</v>
       </c>
       <c r="D10" s="10">
         <f>+SIM②_月5投稿!G34</f>
-        <v>200030.44306925446</v>
       </c>
       <c r="E10" s="10">
         <f>+SIM②_月5投稿!J34</f>
-        <v>160651.33553675146</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -8971,15 +8704,12 @@
       <c r="B11" s="7"/>
       <c r="C11" s="117">
         <f>+SIM②_月5投稿!D35</f>
-        <v>5613.8632704000001</v>
       </c>
       <c r="D11" s="10">
         <f>+SIM②_月5投稿!G35</f>
-        <v>46979.838011993837</v>
       </c>
       <c r="E11" s="10">
         <f>+SIM②_月5投稿!J35</f>
-        <v>37763.622987067356</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -8990,15 +8720,12 @@
       <c r="B12" s="7"/>
       <c r="C12" s="28">
         <f>+IFERROR(C5/C11,0)</f>
-        <v>0</v>
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
-        <v>27.822389018754514</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
-        <v>35.615068158869484</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -9009,15 +8736,12 @@
       <c r="B13" s="7"/>
       <c r="C13" s="28">
         <f>+IFERROR(C6/C12,0)</f>
-        <v>0</v>
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
-        <v>17.562668670699111</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
-        <v>18.720502713745446</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -9039,15 +8763,12 @@
       <c r="B15" s="7"/>
       <c r="C15" s="87">
         <f>+SIM②_月5投稿!D16</f>
-        <v>400</v>
       </c>
       <c r="D15" s="87">
         <f>+SIM②_月5投稿!G16</f>
-        <v>400</v>
       </c>
       <c r="E15" s="87">
         <f>+SIM②_月5投稿!J16</f>
-        <v>400</v>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -9061,15 +8782,12 @@
       <c r="B16" s="7"/>
       <c r="C16" s="87">
         <f>+C17</f>
-        <v>0</v>
       </c>
       <c r="D16" s="87">
         <f>+D17</f>
-        <v>188</v>
       </c>
       <c r="E16" s="87">
         <f>+E17</f>
-        <v>227</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -9089,15 +8807,12 @@
       <c r="B17" s="7"/>
       <c r="C17" s="87">
         <f>+SIM②_月5投稿!D36</f>
-        <v>0</v>
       </c>
       <c r="D17" s="87">
         <f>+SIM②_月5投稿!G36</f>
-        <v>188</v>
       </c>
       <c r="E17" s="87">
         <f>+SIM②_月5投稿!J36</f>
-        <v>227</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -9129,15 +8844,12 @@
       <c r="B18" s="7"/>
       <c r="C18" s="87">
         <f>+SIM②_月5投稿!D37</f>
-        <v>0</v>
       </c>
       <c r="D18" s="87">
         <f>+SIM②_月5投稿!G37</f>
-        <v>0</v>
       </c>
       <c r="E18" s="87">
         <f>+SIM②_月5投稿!J37</f>
-        <v>0</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -9157,7 +8869,6 @@
       </c>
       <c r="X18" s="34">
         <f>+T18*2.5</f>
-        <v>37500000</v>
       </c>
       <c r="Y18" s="35">
         <v>2.5</v>
@@ -9170,15 +8881,12 @@
       <c r="B19" s="7"/>
       <c r="C19" s="87">
         <f>+SIM②_月5投稿!D38</f>
-        <v>0</v>
       </c>
       <c r="D19" s="87">
         <f>+SIM②_月5投稿!G38</f>
-        <v>0</v>
       </c>
       <c r="E19" s="87">
         <f>+SIM②_月5投稿!J38</f>
-        <v>0</v>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -9194,15 +8902,12 @@
       <c r="B20" s="7"/>
       <c r="C20" s="87">
         <f>+SIM②_月5投稿!D39</f>
-        <v>0</v>
       </c>
       <c r="D20" s="87">
         <f>+SIM②_月5投稿!G39</f>
-        <v>0</v>
       </c>
       <c r="E20" s="87">
         <f>+SIM②_月5投稿!J39</f>
-        <v>0</v>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -9229,17 +8934,14 @@
         <v>142</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="90" t="str">
+      <c r="C22" s="90">
         <f>+IFERROR(C4/C16,"--")</f>
-        <v>--</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
-        <v>6952.6134532327833</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
-        <v>5924.9075181068474</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -9253,17 +8955,14 @@
         <v>143</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="90" t="str">
+      <c r="C23" s="90">
         <f>+IFERROR(C5/C16,"--")</f>
-        <v>--</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
-        <v>4388.7836659987406</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
-        <v>3114.3348308821778</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -9292,15 +8991,12 @@
       <c r="B25" s="7"/>
       <c r="C25" s="10">
         <f>+SIM②_月5投稿!E68+C29*C30</f>
-        <v>500308.80000000005</v>
       </c>
       <c r="D25" s="10">
         <f>+SIM②_月5投稿!G68+D29*D30</f>
-        <v>525091.32920776331</v>
       </c>
       <c r="E25" s="10">
         <f>+SIM②_月5投稿!J68+E29*E30</f>
-        <v>406954.00661025441</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -9336,15 +9032,12 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
-        <v>161769.60000000001</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
-        <v>170030.44306925446</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
-        <v>130651.33553675146</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -9359,15 +9052,12 @@
       </c>
       <c r="C30" s="5">
         <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="E30" s="5">
         <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="R30" s="34"/>
       <c r="T30" s="34"/>

--- a/株式会社ワクトリ御中_LINEOA施策提案【SIM】ver1.0.xlsx
+++ b/株式会社ワクトリ御中_LINEOA施策提案【SIM】ver1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B154F7D-5D78-4499-966A-91020CCACFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935E29B2-5ECE-4B1B-969E-7BB111D604E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="SIM②_比較" sheetId="4" r:id="rId4"/>
     <sheet name="SIM考え方" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1" calcId="191029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2540,12 +2540,42 @@
     <xf numFmtId="14" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2567,40 +2597,10 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3051,7 +3051,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="147" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -3084,7 +3084,7 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="138"/>
+      <c r="A9" s="148"/>
       <c r="B9" s="19" t="s">
         <v>8</v>
       </c>
@@ -3114,7 +3114,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="147" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -3142,7 +3142,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="138"/>
+      <c r="A11" s="148"/>
       <c r="B11" s="19" t="s">
         <v>11</v>
       </c>
@@ -3176,10 +3176,10 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="139" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="139"/>
+      <c r="A13" s="149" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="149"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>29</v>
@@ -3222,7 +3222,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="140" t="s">
+      <c r="A14" s="150" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -3261,7 +3261,7 @@
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="141"/>
+      <c r="A15" s="151"/>
       <c r="B15" s="20" t="s">
         <v>35</v>
       </c>
@@ -3310,7 +3310,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="142"/>
+      <c r="A16" s="152"/>
       <c r="B16" s="20" t="s">
         <v>153</v>
       </c>
@@ -3359,7 +3359,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="140" t="s">
+      <c r="A17" s="150" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -3404,7 +3404,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="141"/>
+      <c r="A18" s="151"/>
       <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
@@ -3468,7 +3468,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="141"/>
+      <c r="A19" s="151"/>
       <c r="B19" s="8" t="s">
         <v>116</v>
       </c>
@@ -3529,7 +3529,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="141"/>
+      <c r="A20" s="151"/>
       <c r="B20" s="8" t="s">
         <v>114</v>
       </c>
@@ -3564,7 +3564,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="142"/>
+      <c r="A21" s="152"/>
       <c r="B21" s="8" t="s">
         <v>115</v>
       </c>
@@ -3607,7 +3607,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="143" t="s">
+      <c r="A22" s="153" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3653,7 +3653,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="141"/>
+      <c r="A23" s="151"/>
       <c r="B23" s="6" t="s">
         <v>5</v>
       </c>
@@ -3706,7 +3706,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="141"/>
+      <c r="A24" s="151"/>
       <c r="B24" s="6" t="s">
         <v>116</v>
       </c>
@@ -3759,7 +3759,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="142"/>
+      <c r="A25" s="152"/>
       <c r="B25" s="6" t="s">
         <v>69</v>
       </c>
@@ -3807,10 +3807,10 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="145"/>
+      <c r="B26" s="138"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>21</v>
@@ -3857,10 +3857,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="144" t="s">
+      <c r="A27" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="145"/>
+      <c r="B27" s="138"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0.34100000000000003</v>
@@ -3909,10 +3909,10 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="146" t="s">
+      <c r="A28" s="154" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="147"/>
+      <c r="B28" s="155"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>79904</v>
@@ -3962,10 +3962,10 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="148" t="s">
+      <c r="A29" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="149"/>
+      <c r="B29" s="144"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
@@ -4007,10 +4007,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="136"/>
+      <c r="B30" s="142"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>4</v>
@@ -4049,10 +4049,10 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="145"/>
+      <c r="B31" s="138"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
@@ -4091,10 +4091,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="135" t="s">
+      <c r="A32" s="141" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="136"/>
+      <c r="B32" s="142"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -4138,10 +4138,10 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="145"/>
+      <c r="B33" s="138"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
@@ -4184,10 +4184,10 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="149"/>
+      <c r="B34" s="144"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
@@ -4231,10 +4231,10 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="149"/>
+      <c r="B35" s="144"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
@@ -4278,7 +4278,7 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="145" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="6" t="str">
@@ -4331,7 +4331,7 @@
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="151"/>
+      <c r="A37" s="146"/>
       <c r="B37" s="6" t="str">
         <f>+C9</f>
         <v>-</v>
@@ -4368,7 +4368,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="150" t="s">
+      <c r="A38" s="145" t="s">
         <v>9</v>
       </c>
       <c r="B38" s="6" t="str">
@@ -4410,7 +4410,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="151"/>
+      <c r="A39" s="146"/>
       <c r="B39" s="6" t="str">
         <f>+C11</f>
         <v>-</v>
@@ -4450,10 +4450,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="153"/>
+      <c r="B40" s="140"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="12">+SUM(D36:D39)</f>
@@ -4548,10 +4548,10 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="145"/>
+      <c r="B44" s="138"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>22</v>
@@ -4584,10 +4584,10 @@
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="144" t="s">
+      <c r="A45" s="137" t="s">
         <v>132</v>
       </c>
-      <c r="B45" s="145"/>
+      <c r="B45" s="138"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
         <v>0</v>
@@ -4627,10 +4627,10 @@
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="144" t="s">
+      <c r="A46" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="145"/>
+      <c r="B46" s="138"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>22</v>
@@ -4663,10 +4663,10 @@
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="144" t="s">
+      <c r="A47" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="145"/>
+      <c r="B47" s="138"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>22</v>
@@ -4699,10 +4699,10 @@
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="144" t="s">
+      <c r="A48" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="145"/>
+      <c r="B48" s="138"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>22</v>
@@ -4735,10 +4735,10 @@
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="152" t="s">
+      <c r="A49" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="B49" s="153"/>
+      <c r="B49" s="140"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>22</v>
@@ -4771,10 +4771,10 @@
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="152" t="s">
+      <c r="A50" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="153"/>
+      <c r="B50" s="140"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>22</v>
@@ -4807,10 +4807,10 @@
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="154" t="s">
+      <c r="A51" s="135" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="155"/>
+      <c r="B51" s="136"/>
       <c r="C51" s="110">
         <f>+C45</f>
         <v>0</v>
@@ -4864,10 +4864,10 @@
       </c>
     </row>
     <row r="54" spans="1:14" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="145"/>
+      <c r="B54" s="138"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
@@ -4904,10 +4904,10 @@
       </c>
     </row>
     <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="137" t="s">
         <v>132</v>
       </c>
-      <c r="B55" s="145"/>
+      <c r="B55" s="138"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
@@ -4941,10 +4941,10 @@
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B56" s="145"/>
+      <c r="B56" s="138"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>22</v>
@@ -4977,10 +4977,10 @@
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="144" t="s">
+      <c r="A57" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="B57" s="145"/>
+      <c r="B57" s="138"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>22</v>
@@ -5013,10 +5013,10 @@
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="144" t="s">
+      <c r="A58" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="145"/>
+      <c r="B58" s="138"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>22</v>
@@ -5049,10 +5049,10 @@
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="B59" s="153"/>
+      <c r="B59" s="140"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
@@ -5083,10 +5083,10 @@
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="152" t="s">
+      <c r="A60" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="153"/>
+      <c r="B60" s="140"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -5099,10 +5099,10 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="154" t="s">
+      <c r="A61" s="135" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="155"/>
+      <c r="B61" s="136"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
@@ -5537,6 +5537,29 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
@@ -5549,29 +5572,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6276,7 +6276,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="147" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -6309,7 +6309,7 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="138"/>
+      <c r="A9" s="148"/>
       <c r="B9" s="19" t="s">
         <v>8</v>
       </c>
@@ -6339,7 +6339,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="147" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -6367,7 +6367,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="138"/>
+      <c r="A11" s="148"/>
       <c r="B11" s="19" t="s">
         <v>11</v>
       </c>
@@ -6401,10 +6401,10 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="139" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="139"/>
+      <c r="A13" s="149" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="149"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>29</v>
@@ -6447,7 +6447,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="140" t="s">
+      <c r="A14" s="150" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -6456,54 +6456,68 @@
       <c r="C14" s="99"/>
       <c r="D14" s="42">
         <f>+H8</f>
+        <v>85887</v>
       </c>
       <c r="E14" s="43">
         <f>+D14</f>
+        <v>85887</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" ref="F14:J14" si="0">+E14</f>
+        <v>85887</v>
       </c>
       <c r="G14" s="43">
         <f t="shared" si="0"/>
+        <v>85887</v>
       </c>
       <c r="H14" s="43">
         <f t="shared" si="0"/>
+        <v>85887</v>
       </c>
       <c r="I14" s="43">
         <f t="shared" si="0"/>
+        <v>85887</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="0"/>
+        <v>85887</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="141"/>
+      <c r="A15" s="151"/>
       <c r="B15" s="20" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="99"/>
       <c r="D15" s="42">
         <f t="shared" ref="D15" si="1">+H9</f>
+        <v>0</v>
       </c>
       <c r="E15" s="43">
         <f t="shared" ref="E15:J16" si="2">+D15</f>
+        <v>0</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
@@ -6521,31 +6535,38 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="142"/>
+      <c r="A16" s="152"/>
       <c r="B16" s="20" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="99"/>
       <c r="D16" s="42">
         <f>H10</f>
+        <v>400</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -6563,7 +6584,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="140" t="s">
+      <c r="A17" s="150" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -6608,7 +6629,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="141"/>
+      <c r="A18" s="151"/>
       <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
@@ -6672,7 +6693,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="141"/>
+      <c r="A19" s="151"/>
       <c r="B19" s="8" t="s">
         <v>116</v>
       </c>
@@ -6726,13 +6747,14 @@
       </c>
       <c r="Y19" s="34">
         <f>+U19*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Z19" s="35">
         <v>2.5</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="141"/>
+      <c r="A20" s="151"/>
       <c r="B20" s="8" t="s">
         <v>114</v>
       </c>
@@ -6767,7 +6789,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="142"/>
+      <c r="A21" s="152"/>
       <c r="B21" s="8" t="s">
         <v>115</v>
       </c>
@@ -6810,7 +6832,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="143" t="s">
+      <c r="A22" s="153" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -6856,7 +6878,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="141"/>
+      <c r="A23" s="151"/>
       <c r="B23" s="6" t="s">
         <v>5</v>
       </c>
@@ -6866,21 +6888,27 @@
       </c>
       <c r="E23" s="46">
         <f>IF(E18=FALSE,0,E15*$P$18*0.08*0.08+(E14-E15)*$P$19*0.12*0.12)</f>
+        <v>680.22504000000004</v>
       </c>
       <c r="F23" s="46">
         <f>IF(F18=FALSE,0,F15*$P$18*0.08*0.08+(F14-F15)*$P$19*0.12*0.12)</f>
+        <v>680.22504000000004</v>
       </c>
       <c r="G23" s="63">
         <f t="shared" ref="G23:J23" si="3">F23*1.01</f>
+        <v>687.02729040000008</v>
       </c>
       <c r="H23" s="63">
         <f t="shared" si="3"/>
+        <v>693.89756330400007</v>
       </c>
       <c r="I23" s="63">
         <f t="shared" si="3"/>
+        <v>700.83653893704013</v>
       </c>
       <c r="J23" s="63">
         <f t="shared" si="3"/>
+        <v>707.84490432641053</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
@@ -6903,7 +6931,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="141"/>
+      <c r="A24" s="151"/>
       <c r="B24" s="6" t="s">
         <v>116</v>
       </c>
@@ -6913,21 +6941,27 @@
       </c>
       <c r="E24" s="46">
         <f t="shared" ref="E24:J24" si="4">IF(E19=FALSE,0,$H$10*0.8*0.45)</f>
+        <v>0</v>
       </c>
       <c r="F24" s="63">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="G24" s="63">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="H24" s="63">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="I24" s="63">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="J24" s="63">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
@@ -6950,7 +6984,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="142"/>
+      <c r="A25" s="152"/>
       <c r="B25" s="6" t="s">
         <v>69</v>
       </c>
@@ -6960,21 +6994,27 @@
       </c>
       <c r="E25" s="46">
         <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" ref="F25:J25" si="5">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="G25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="I25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="J25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="7"/>
@@ -6992,31 +7032,37 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="145"/>
+      <c r="B26" s="138"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="46">
         <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
+        <v>1109.66004</v>
       </c>
       <c r="F26" s="46">
         <f t="shared" ref="F26:J26" si="6">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>1109.66004</v>
       </c>
       <c r="G26" s="46">
         <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>1116.4622904</v>
       </c>
       <c r="H26" s="46">
         <f t="shared" si="6"/>
+        <v>1123.3325633040001</v>
       </c>
       <c r="I26" s="46">
         <f t="shared" si="6"/>
+        <v>1130.2715389370401</v>
       </c>
       <c r="J26" s="46">
         <f t="shared" si="6"/>
+        <v>1137.2799043264106</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
@@ -7036,31 +7082,36 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="144" t="s">
+      <c r="A27" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="145"/>
+      <c r="B27" s="138"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
-        <v>0.341</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="E27" s="47">
-        <v>0.341</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="F27" s="47">
         <f>ROUND(E27*1.02,3)</f>
+        <v>0.34799999999999998</v>
       </c>
       <c r="G27" s="47">
         <f>ROUND(F27*1.02,3)</f>
+        <v>0.35499999999999998</v>
       </c>
       <c r="H27" s="47">
         <f>ROUND(G27*1.02,3)</f>
+        <v>0.36199999999999999</v>
       </c>
       <c r="I27" s="47">
         <f>ROUND(H27*1.02,3)</f>
+        <v>0.36899999999999999</v>
       </c>
       <c r="J27" s="47">
         <f>ROUND(I27*1.02,3)</f>
+        <v>0.376</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
@@ -7083,31 +7134,37 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="146" t="s">
+      <c r="A28" s="154" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="147"/>
+      <c r="B28" s="155"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>79904</v>
       </c>
       <c r="E28" s="49">
         <f>+D28+E26</f>
+        <v>81013.660040000002</v>
       </c>
       <c r="F28" s="49">
         <f t="shared" ref="F28:J28" si="7">+E28+F26</f>
+        <v>82123.320080000005</v>
       </c>
       <c r="G28" s="49">
         <f t="shared" si="7"/>
+        <v>83239.782370400004</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="7"/>
+        <v>84363.114933703997</v>
       </c>
       <c r="I28" s="49">
         <f t="shared" si="7"/>
+        <v>85493.386472641039</v>
       </c>
       <c r="J28" s="49">
         <f t="shared" si="7"/>
+        <v>86630.666376967449</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
@@ -7130,31 +7187,38 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="148" t="s">
+      <c r="A29" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="149"/>
+      <c r="B29" s="144"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
+        <v>52656.736000000004</v>
       </c>
       <c r="E29" s="50">
         <f>+E28*(1-E27)</f>
+        <v>53388.001966360003</v>
       </c>
       <c r="F29" s="50">
         <f t="shared" ref="F29:J29" si="8">+F28*(1-F27)</f>
+        <v>53544.404692160002</v>
       </c>
       <c r="G29" s="50">
         <f t="shared" si="8"/>
+        <v>53689.659628908004</v>
       </c>
       <c r="H29" s="50">
         <f t="shared" si="8"/>
+        <v>53823.667327703151</v>
       </c>
       <c r="I29" s="50">
         <f t="shared" si="8"/>
+        <v>53946.326864236493</v>
       </c>
       <c r="J29" s="50">
         <f t="shared" si="8"/>
+        <v>54057.535819227691</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -7168,10 +7232,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="136"/>
+      <c r="B30" s="142"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>4</v>
@@ -7210,31 +7274,38 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="145"/>
+      <c r="B31" s="138"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
+        <v>6044.9932928000007</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>24387.596587831689</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>24459.041227854945</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>24525.393566757488</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>19669.286541088761</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>19714.111163617403</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>19754.751292955654</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -7245,10 +7316,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="135" t="s">
+      <c r="A32" s="141" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="136"/>
+      <c r="B32" s="142"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -7284,6 +7355,7 @@
       </c>
       <c r="Q32" s="73">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
@@ -7291,31 +7363,37 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="145"/>
+      <c r="B33" s="138"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
       </c>
       <c r="E33" s="63">
         <f t="shared" ref="E33:J33" si="9">+(E26-E24)*E32*$P$26*$P$27*$P$36</f>
+        <v>706.72417008534012</v>
       </c>
       <c r="F33" s="63">
         <f t="shared" si="9"/>
+        <v>706.72417008534012</v>
       </c>
       <c r="G33" s="63">
         <f t="shared" si="9"/>
+        <v>711.05641112796854</v>
       </c>
       <c r="H33" s="63">
         <f t="shared" si="9"/>
+        <v>715.43197458102338</v>
       </c>
       <c r="I33" s="63">
         <f t="shared" si="9"/>
+        <v>719.85129366860861</v>
       </c>
       <c r="J33" s="63">
         <f t="shared" si="9"/>
+        <v>724.31480594706977</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -7327,34 +7405,42 @@
       </c>
       <c r="Q33" s="73">
         <f t="shared" ref="Q33:Q35" si="10">+IF(P33=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="149"/>
+      <c r="B34" s="144"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
+        <v>210626.94400000002</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E26*E32</f>
+        <v>219100.30806544001</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F26*F32</f>
+        <v>219725.91896864001</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G26*G32</f>
+        <v>220340.94996763204</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H26*H32</f>
+        <v>177852.39826517008</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I26*I32</f>
+        <v>178279.60366024199</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J26*J32</f>
+        <v>178670.51414316069</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -7366,34 +7452,42 @@
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="10"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="149"/>
+      <c r="B35" s="144"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
+        <v>6165.8931586560011</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
+        <v>51443.357553729918</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" ref="F35:J35" si="11">+F31+F33+1.05*(F31+F33)</f>
+        <v>51589.819065777585</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="11"/>
+        <v>51734.722454665185</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="11"/>
+        <v>41788.672957123061</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="11"/>
+        <v>41889.623037436322</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="11"/>
+        <v>41982.08550275059</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -7405,14 +7499,16 @@
       </c>
       <c r="Q35" s="73">
         <f t="shared" si="10"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="6" t="str">
         <f>+C8</f>
+        <v>応募</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="11">
@@ -7420,24 +7516,31 @@
       </c>
       <c r="E36" s="111">
         <f>ROUND(E35*0.004,0)</f>
+        <v>206</v>
       </c>
       <c r="F36" s="111">
         <f>ROUND(F35*0.0045,0)</f>
+        <v>232</v>
       </c>
       <c r="G36" s="111">
         <f>ROUND(G35*0.0055,0)</f>
+        <v>285</v>
       </c>
       <c r="H36" s="111">
         <f>ROUND(H35*0.0065,0)</f>
+        <v>272</v>
       </c>
       <c r="I36" s="111">
         <f>ROUND(I35*0.0075,0)</f>
+        <v>314</v>
       </c>
       <c r="J36" s="111">
         <f>ROUND(J35*0.009,0)</f>
+        <v>378</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
+        <v>1687</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
@@ -7448,13 +7551,15 @@
       </c>
       <c r="P36" s="74">
         <f>1*(Q32*Q33*Q34*Q35)</f>
+        <v>1.4641000000000006</v>
       </c>
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="151"/>
-      <c r="B37" s="6">
+      <c r="A37" s="146"/>
+      <c r="B37" s="6" t="str">
         <f>+C9</f>
+        <v>-</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
@@ -7480,6 +7585,7 @@
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
+        <v>0</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
@@ -7487,11 +7593,12 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="150" t="s">
+      <c r="A38" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="6" t="str">
         <f>+C10</f>
+        <v>-</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="11">
@@ -7517,6 +7624,7 @@
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
+        <v>0</v>
       </c>
       <c r="L38" s="7"/>
       <c r="N38" s="69" t="s">
@@ -7527,9 +7635,10 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="151"/>
-      <c r="B39" s="6">
+      <c r="A39" s="146"/>
+      <c r="B39" s="6" t="str">
         <f>+C11</f>
+        <v>-</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="11">
@@ -7555,6 +7664,7 @@
       </c>
       <c r="K39" s="115">
         <f>SUM(E39:J39)</f>
+        <v>0</v>
       </c>
       <c r="L39" s="7"/>
       <c r="N39" s="69" t="s">
@@ -7565,34 +7675,42 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="153"/>
+      <c r="B40" s="140"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="12">+SUM(D36:D39)</f>
+        <v>0</v>
       </c>
       <c r="E40" s="10">
         <f t="shared" si="12"/>
+        <v>206</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="12"/>
+        <v>232</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="12"/>
+        <v>285</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="12"/>
+        <v>272</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="12"/>
+        <v>314</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="12"/>
+        <v>378</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
+        <v>1687</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -7603,24 +7721,31 @@
       </c>
       <c r="D41" s="18">
         <f t="shared" ref="D41" si="13">+IFERROR(D40/D35,0)</f>
+        <v>0</v>
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
+        <v>4.0044042573396128E-3</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="14">+IFERROR(F40/F35,0)</f>
+        <v>4.4970113134957393E-3</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="14"/>
+        <v>5.5088726966640968E-3</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="14"/>
+        <v>6.5089408385636816E-3</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="14"/>
+        <v>7.4958898464992504E-3</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="14"/>
+        <v>9.0038404589318013E-3</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>118</v>
@@ -7648,63 +7773,77 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="145"/>
+      <c r="B44" s="138"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
+        <v>567300.92419632</v>
       </c>
       <c r="F44" s="31">
         <f t="shared" ref="F44:J44" si="15">+F75*F76</f>
+        <v>569177.75690591999</v>
       </c>
       <c r="G44" s="31">
         <f t="shared" si="15"/>
+        <v>571022.84990289609</v>
       </c>
       <c r="H44" s="31">
         <f t="shared" si="15"/>
+        <v>443557.19479551027</v>
       </c>
       <c r="I44" s="31">
         <f t="shared" si="15"/>
+        <v>444838.81098072598</v>
       </c>
       <c r="J44" s="31">
         <f t="shared" si="15"/>
+        <v>446011.5424294821</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="144" t="s">
+      <c r="A45" s="137" t="s">
         <v>132</v>
       </c>
-      <c r="B45" s="145"/>
+      <c r="B45" s="138"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
+        <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
+        <v>265000</v>
       </c>
       <c r="E45" s="27">
         <f t="shared" ref="E45:J45" si="16">SUM(E65:E68)+SUM(E71:E72)</f>
+        <v>45000</v>
       </c>
       <c r="F45" s="27">
         <f t="shared" si="16"/>
+        <v>45000</v>
       </c>
       <c r="G45" s="27">
         <f t="shared" si="16"/>
+        <v>45000</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="16"/>
+        <v>45000</v>
       </c>
       <c r="I45" s="27">
         <f t="shared" si="16"/>
+        <v>45000</v>
       </c>
       <c r="J45" s="27">
         <f t="shared" si="16"/>
+        <v>45000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
@@ -7713,183 +7852,221 @@
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="144" t="s">
+      <c r="A46" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="145"/>
+      <c r="B46" s="138"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E46" s="28">
         <f t="shared" ref="E46:J46" si="17">+SUM(E65:E67)/(E28-D28)</f>
+        <v>27.035307137850914</v>
       </c>
       <c r="F46" s="28">
         <f t="shared" si="17"/>
+        <v>27.035307137850914</v>
       </c>
       <c r="G46" s="28">
         <f t="shared" si="17"/>
+        <v>26.870589591746796</v>
       </c>
       <c r="H46" s="28">
         <f t="shared" si="17"/>
+        <v>26.70624976076785</v>
       </c>
       <c r="I46" s="28">
         <f t="shared" si="17"/>
+        <v>26.542294454493064</v>
       </c>
       <c r="J46" s="28">
         <f t="shared" si="17"/>
+        <v>26.378730412693315</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="144" t="s">
+      <c r="A47" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="145"/>
+      <c r="B47" s="138"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="18">+E51/E35</f>
+        <v>11.902429260314189</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="18"/>
+        <v>11.905018626307578</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="18"/>
+        <v>11.907338450355331</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="18"/>
+        <v>11.69113925433312</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="18"/>
+        <v>11.693559775960793</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
+        <v>11.69573966012984</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="144" t="s">
+      <c r="A48" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="145"/>
+      <c r="B48" s="138"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="19">+SUM(E36:E39)/E35</f>
+        <v>4.0044042573396128E-3</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="19"/>
+        <v>4.4970113134957393E-3</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="19"/>
+        <v>5.5088726966640968E-3</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="19"/>
+        <v>6.5089408385636816E-3</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="19"/>
+        <v>7.4958898464992504E-3</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="19"/>
+        <v>9.0038404589318013E-3</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="152" t="s">
+      <c r="A49" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="B49" s="153"/>
+      <c r="B49" s="140"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
+        <v>2972.3345834772817</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="20">+IFERROR(F51/SUM(F36:F39),0)</f>
+        <v>2647.3179176979311</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="20"/>
+        <v>2161.4836838698106</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="20"/>
+        <v>1796.1661573364347</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="20"/>
+        <v>1559.996213314414</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="20"/>
+        <v>1298.9723344695294</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="152" t="s">
+      <c r="A50" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="153"/>
+      <c r="B50" s="140"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>22</v>
       </c>
       <c r="E50" s="65">
         <f>+E36*$D$8+E38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="F50" s="65">
         <f t="shared" ref="F50:J50" si="21">+F36*$D$8+F38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="G50" s="65">
         <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="H50" s="65">
         <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="I50" s="65">
         <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="J50" s="65">
         <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="154" t="s">
+      <c r="A51" s="135" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="155"/>
+      <c r="B51" s="136"/>
       <c r="C51" s="110">
         <f>+C45</f>
+        <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
+        <v>265000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
+        <v>612300.92419632</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="22">SUM(F45,F50)+F44</f>
+        <v>614177.75690591999</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="22"/>
+        <v>616022.84990289609</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="22"/>
+        <v>488557.19479551027</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="22"/>
+        <v>489838.81098072598</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
+        <v>491011.5424294821</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -7912,31 +8089,38 @@
       </c>
     </row>
     <row r="54" spans="1:14" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="145"/>
+      <c r="B54" s="138"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
+        <v>541880.83200000005</v>
       </c>
       <c r="E54" s="28">
         <f t="shared" ref="E54:J54" si="23">+E75*E76</f>
+        <v>567300.92419632</v>
       </c>
       <c r="F54" s="28">
         <f t="shared" si="23"/>
+        <v>569177.75690591999</v>
       </c>
       <c r="G54" s="28">
         <f t="shared" si="23"/>
+        <v>571022.84990289609</v>
       </c>
       <c r="H54" s="28">
         <f t="shared" si="23"/>
+        <v>443557.19479551027</v>
       </c>
       <c r="I54" s="28">
         <f t="shared" si="23"/>
+        <v>444838.81098072598</v>
       </c>
       <c r="J54" s="28">
         <f t="shared" si="23"/>
+        <v>446011.5424294821</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
@@ -7945,158 +8129,189 @@
       </c>
     </row>
     <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="137" t="s">
         <v>132</v>
       </c>
-      <c r="B55" s="145"/>
+      <c r="B55" s="138"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
+        <v>265000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
+        <v>962300.92419632</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="24">SUM(F65:F72)+F54</f>
+        <v>964177.75690591999</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="24"/>
+        <v>966022.84990289609</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="24"/>
+        <v>838557.19479551027</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="24"/>
+        <v>839838.81098072603</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="24"/>
+        <v>841011.5424294821</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B56" s="145"/>
+      <c r="B56" s="138"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E56" s="28">
         <f>+SUM(E65:E67)/(E28-D28)</f>
+        <v>27.035307137850914</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" ref="F56:J56" si="25">+SUM(F65:F67)/(F28-E28)</f>
+        <v>27.035307137850914</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="25"/>
+        <v>26.870589591746796</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="25"/>
+        <v>26.70624976076785</v>
       </c>
       <c r="I56" s="28">
         <f t="shared" si="25"/>
+        <v>26.542294454493064</v>
       </c>
       <c r="J56" s="28">
         <f t="shared" si="25"/>
+        <v>26.378730412693315</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="144" t="s">
+      <c r="A57" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="B57" s="145"/>
+      <c r="B57" s="138"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
+        <v>18.706028726667899</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="26">+F61/F35</f>
+        <v>18.689302935460635</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="26"/>
+        <v>18.672620709416503</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="26"/>
+        <v>20.066614598073151</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="26"/>
+        <v>20.04885100613512</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="26"/>
+        <v>20.032628973955582</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="144" t="s">
+      <c r="A58" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="145"/>
+      <c r="B58" s="138"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="27">+SUM(E36:E39)/E35</f>
+        <v>4.0044042573396128E-3</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="27"/>
+        <v>4.4970113134957393E-3</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="27"/>
+        <v>5.5088726966640968E-3</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="27"/>
+        <v>6.5089408385636816E-3</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="27"/>
+        <v>7.4958898464992504E-3</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="27"/>
+        <v>9.0038404589318013E-3</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="B59" s="153"/>
+      <c r="B59" s="140"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
+        <v>4671.3637096908742</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="28">+IFERROR(F55/F40,0)</f>
+        <v>4155.9386073531032</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="28"/>
+        <v>3389.5538593084075</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="28"/>
+        <v>3082.9308632187876</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="28"/>
+        <v>2674.6458948430763</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="28"/>
+        <v>2224.8982603954555</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="152" t="s">
+      <c r="A60" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="153"/>
+      <c r="B60" s="140"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -8109,31 +8324,38 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="154" t="s">
+      <c r="A61" s="135" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="155"/>
+      <c r="B61" s="136"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
+        <v>265000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
+        <v>962300.92419632</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="29">+SUM(F65:F72)+F54</f>
+        <v>964177.75690591999</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="29"/>
+        <v>966022.84990289609</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="29"/>
+        <v>838557.19479551027</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="29"/>
+        <v>839838.81098072603</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="29"/>
+        <v>841011.5424294821</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -8259,21 +8481,27 @@
       </c>
       <c r="E68" s="28">
         <f t="shared" ref="E68:J68" si="30">IF(E34&lt;5000,5000,15000)</f>
+        <v>15000</v>
       </c>
       <c r="F68" s="28">
         <f t="shared" si="30"/>
+        <v>15000</v>
       </c>
       <c r="G68" s="28">
         <f t="shared" si="30"/>
+        <v>15000</v>
       </c>
       <c r="H68" s="28">
         <f t="shared" si="30"/>
+        <v>15000</v>
       </c>
       <c r="I68" s="28">
         <f t="shared" si="30"/>
+        <v>15000</v>
       </c>
       <c r="J68" s="28">
         <f t="shared" si="30"/>
+        <v>15000</v>
       </c>
       <c r="N68" s="69" t="s">
         <v>190</v>
@@ -8294,25 +8522,25 @@
         <v>0</v>
       </c>
       <c r="D69" s="51">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="E69" s="28">
-        <v>270000</v>
+        <v>350000</v>
       </c>
       <c r="F69" s="28">
-        <v>270000</v>
+        <v>350000</v>
       </c>
       <c r="G69" s="28">
-        <v>270000</v>
+        <v>350000</v>
       </c>
       <c r="H69" s="28">
-        <v>270000</v>
+        <v>350000</v>
       </c>
       <c r="I69" s="28">
-        <v>270000</v>
+        <v>350000</v>
       </c>
       <c r="J69" s="28">
-        <v>270000</v>
+        <v>350000</v>
       </c>
       <c r="N69" s="69" t="s">
         <v>200</v>
@@ -8427,24 +8655,31 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
+        <v>265000</v>
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="31">SUM(E65:E72)+E54</f>
+        <v>962300.92419632</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="31"/>
+        <v>964177.75690591999</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="31"/>
+        <v>966022.84990289609</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="31"/>
+        <v>838557.19479551027</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="31"/>
+        <v>839838.81098072603</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="31"/>
+        <v>841011.5424294821</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8465,24 +8700,31 @@
       </c>
       <c r="D75" s="41">
         <f t="shared" ref="D75:J75" si="32">+IF(D34&lt;30001,0,D34-30000)</f>
+        <v>180626.94400000002</v>
       </c>
       <c r="E75" s="41">
         <f t="shared" si="32"/>
+        <v>189100.30806544001</v>
       </c>
       <c r="F75" s="41">
         <f t="shared" si="32"/>
+        <v>189725.91896864001</v>
       </c>
       <c r="G75" s="41">
         <f t="shared" si="32"/>
+        <v>190340.94996763204</v>
       </c>
       <c r="H75" s="41">
         <f t="shared" si="32"/>
+        <v>147852.39826517008</v>
       </c>
       <c r="I75" s="41">
         <f t="shared" si="32"/>
+        <v>148279.60366024199</v>
       </c>
       <c r="J75" s="41">
         <f t="shared" si="32"/>
+        <v>148670.51414316069</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8491,28 +8733,58 @@
       </c>
       <c r="D76" s="5">
         <f t="shared" ref="D76:J76" si="33">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="F76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="G76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="H76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="J76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
@@ -8525,29 +8797,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8598,14 +8847,17 @@
         <v>140</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="86">
+      <c r="C4" s="86" t="str">
         <f>+SIM②_月5投稿!D24</f>
+        <v>--</v>
       </c>
       <c r="D4" s="28">
         <f>+SIM②_月5投稿!G51</f>
+        <v>616022.84990289609</v>
       </c>
       <c r="E4" s="28">
         <f>+SIM②_月5投稿!J51</f>
+        <v>491011.5424294821</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -8614,14 +8866,17 @@
         <v>141</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="86">
+      <c r="C5" s="86" t="str">
         <f>+SIM②_月5投稿!D25</f>
+        <v>--</v>
       </c>
       <c r="D5" s="28">
         <f>+SIM②_月5投稿!G61</f>
+        <v>966022.84990289609</v>
       </c>
       <c r="E5" s="28">
         <f>+SIM②_月5投稿!J61</f>
+        <v>841011.5424294821</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -8632,12 +8887,15 @@
       <c r="B6" s="7"/>
       <c r="C6" s="117">
         <f>+SIM②_月5投稿!D28</f>
+        <v>79904</v>
       </c>
       <c r="D6" s="87">
         <f>+SIM②_月5投稿!G28</f>
+        <v>83239.782370400004</v>
       </c>
       <c r="E6" s="87">
         <f>+SIM②_月5投稿!J28</f>
+        <v>86630.666376967449</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -8648,12 +8906,15 @@
       <c r="B7" s="7"/>
       <c r="C7" s="88">
         <f>+SIM②_月5投稿!D27</f>
+        <v>0.34100000000000003</v>
       </c>
       <c r="D7" s="89">
         <f>+SIM②_月5投稿!G27</f>
+        <v>0.35499999999999998</v>
       </c>
       <c r="E7" s="89">
         <f>+SIM②_月5投稿!J27</f>
+        <v>0.376</v>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -8664,12 +8925,15 @@
       <c r="B8" s="7"/>
       <c r="C8" s="117">
         <f>+SIM②_月5投稿!D29</f>
+        <v>52656.736000000004</v>
       </c>
       <c r="D8" s="10">
         <f>+SIM②_月5投稿!G29</f>
+        <v>53689.659628908004</v>
       </c>
       <c r="E8" s="10">
         <f>+SIM②_月5投稿!J29</f>
+        <v>54057.535819227691</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -8688,12 +8952,15 @@
       <c r="B10" s="7"/>
       <c r="C10" s="117">
         <f>+SIM②_月5投稿!D34</f>
+        <v>210626.94400000002</v>
       </c>
       <c r="D10" s="10">
         <f>+SIM②_月5投稿!G34</f>
+        <v>220340.94996763204</v>
       </c>
       <c r="E10" s="10">
         <f>+SIM②_月5投稿!J34</f>
+        <v>178670.51414316069</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -8704,12 +8971,15 @@
       <c r="B11" s="7"/>
       <c r="C11" s="117">
         <f>+SIM②_月5投稿!D35</f>
+        <v>6165.8931586560011</v>
       </c>
       <c r="D11" s="10">
         <f>+SIM②_月5投稿!G35</f>
+        <v>51734.722454665185</v>
       </c>
       <c r="E11" s="10">
         <f>+SIM②_月5投稿!J35</f>
+        <v>41982.08550275059</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -8720,12 +8990,15 @@
       <c r="B12" s="7"/>
       <c r="C12" s="28">
         <f>+IFERROR(C5/C11,0)</f>
+        <v>0</v>
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
+        <v>11.907338450355331</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
+        <v>11.69573966012984</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -8736,12 +9009,15 @@
       <c r="B13" s="7"/>
       <c r="C13" s="28">
         <f>+IFERROR(C6/C12,0)</f>
+        <v>0</v>
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
+        <v>18.672620709416503</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
+        <v>20.032628973955582</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -8763,12 +9039,15 @@
       <c r="B15" s="7"/>
       <c r="C15" s="87">
         <f>+SIM②_月5投稿!D16</f>
+        <v>400</v>
       </c>
       <c r="D15" s="87">
         <f>+SIM②_月5投稿!G16</f>
+        <v>400</v>
       </c>
       <c r="E15" s="87">
         <f>+SIM②_月5投稿!J16</f>
+        <v>400</v>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -8782,12 +9061,15 @@
       <c r="B16" s="7"/>
       <c r="C16" s="87">
         <f>+C17</f>
+        <v>0</v>
       </c>
       <c r="D16" s="87">
         <f>+D17</f>
+        <v>285</v>
       </c>
       <c r="E16" s="87">
         <f>+E17</f>
+        <v>378</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -8807,12 +9089,15 @@
       <c r="B17" s="7"/>
       <c r="C17" s="87">
         <f>+SIM②_月5投稿!D36</f>
+        <v>0</v>
       </c>
       <c r="D17" s="87">
         <f>+SIM②_月5投稿!G36</f>
+        <v>285</v>
       </c>
       <c r="E17" s="87">
         <f>+SIM②_月5投稿!J36</f>
+        <v>378</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -8844,12 +9129,15 @@
       <c r="B18" s="7"/>
       <c r="C18" s="87">
         <f>+SIM②_月5投稿!D37</f>
+        <v>0</v>
       </c>
       <c r="D18" s="87">
         <f>+SIM②_月5投稿!G37</f>
+        <v>0</v>
       </c>
       <c r="E18" s="87">
         <f>+SIM②_月5投稿!J37</f>
+        <v>0</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -8869,6 +9157,7 @@
       </c>
       <c r="X18" s="34">
         <f>+T18*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Y18" s="35">
         <v>2.5</v>
@@ -8881,12 +9170,15 @@
       <c r="B19" s="7"/>
       <c r="C19" s="87">
         <f>+SIM②_月5投稿!D38</f>
+        <v>0</v>
       </c>
       <c r="D19" s="87">
         <f>+SIM②_月5投稿!G38</f>
+        <v>0</v>
       </c>
       <c r="E19" s="87">
         <f>+SIM②_月5投稿!J38</f>
+        <v>0</v>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -8902,12 +9194,15 @@
       <c r="B20" s="7"/>
       <c r="C20" s="87">
         <f>+SIM②_月5投稿!D39</f>
+        <v>0</v>
       </c>
       <c r="D20" s="87">
         <f>+SIM②_月5投稿!G39</f>
+        <v>0</v>
       </c>
       <c r="E20" s="87">
         <f>+SIM②_月5投稿!J39</f>
+        <v>0</v>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -8934,14 +9229,17 @@
         <v>142</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="90">
+      <c r="C22" s="90" t="str">
         <f>+IFERROR(C4/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
+        <v>2161.4836838698106</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
+        <v>1298.9723344695294</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -8955,14 +9253,17 @@
         <v>143</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="90">
+      <c r="C23" s="90" t="str">
         <f>+IFERROR(C5/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
+        <v>3389.5538593084075</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
+        <v>2224.8982603954555</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -8991,12 +9292,15 @@
       <c r="B25" s="7"/>
       <c r="C25" s="10">
         <f>+SIM②_月5投稿!E68+C29*C30</f>
+        <v>556880.83200000005</v>
       </c>
       <c r="D25" s="10">
         <f>+SIM②_月5投稿!G68+D29*D30</f>
+        <v>586022.84990289609</v>
       </c>
       <c r="E25" s="10">
         <f>+SIM②_月5投稿!J68+E29*E30</f>
+        <v>461011.5424294821</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -9032,12 +9336,15 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
+        <v>180626.94400000002</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
+        <v>190340.94996763204</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
+        <v>148670.51414316069</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -9052,12 +9359,15 @@
       </c>
       <c r="C30" s="5">
         <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E30" s="5">
         <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="R30" s="34"/>
       <c r="T30" s="34"/>
@@ -9489,6 +9799,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C357D3FFD3874644B9B63D306D91E343" ma:contentTypeVersion="5" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="bfcf90751a1be541a10eb2cf2bfdf12b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="79deb97c-193b-473b-ac92-dc976e68b6a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9df8bde209fb52400f7491d2ba74e6ee" ns3:_="">
     <xsd:import namespace="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
@@ -9638,24 +9965,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2519B170-E350-4E75-B7A7-F72CE5062C7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9671,28 +10005,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/株式会社ワクトリ御中_LINEOA施策提案【SIM】ver1.0.xlsx
+++ b/株式会社ワクトリ御中_LINEOA施策提案【SIM】ver1.0.xlsx
@@ -19,7 +19,7 @@
     <sheet name="SIM②_比較" sheetId="4" r:id="rId4"/>
     <sheet name="SIM考え方" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr fullCalcOnLoad="1" calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2986,8 +2986,10 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="56" t="s">
-        <v>163</v>
+      <c r="A4" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">株式会社ワクトリ御中_LINEOA施策提案【SIM】プラン①（月3投稿）：ポップアップ</t>
+        </is>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -3231,31 +3233,24 @@
       <c r="C14" s="99"/>
       <c r="D14" s="42">
         <f>+H8</f>
-        <v>85887</v>
       </c>
       <c r="E14" s="43">
         <f>+D14</f>
-        <v>85887</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" ref="F14:J14" si="0">+E14</f>
-        <v>85887</v>
       </c>
       <c r="G14" s="43">
         <f t="shared" si="0"/>
-        <v>85887</v>
       </c>
       <c r="H14" s="43">
         <f t="shared" si="0"/>
-        <v>85887</v>
       </c>
       <c r="I14" s="43">
         <f t="shared" si="0"/>
-        <v>85887</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="0"/>
-        <v>85887</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
@@ -3268,31 +3263,24 @@
       <c r="C15" s="99"/>
       <c r="D15" s="42">
         <f t="shared" ref="D15" si="1">+H9</f>
-        <v>0</v>
       </c>
       <c r="E15" s="43">
         <f t="shared" ref="E15:J16" si="2">+D15</f>
-        <v>0</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="H15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="I15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
@@ -3317,31 +3305,24 @@
       <c r="C16" s="99"/>
       <c r="D16" s="42">
         <f>H10</f>
-        <v>400</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="2"/>
-        <v>400</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -3477,22 +3458,22 @@
         <v>0</v>
       </c>
       <c r="E19" s="57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="14"/>
       <c r="L19" s="9"/>
@@ -3522,7 +3503,6 @@
       </c>
       <c r="Y19" s="34">
         <f>+U19*2.5</f>
-        <v>37500000</v>
       </c>
       <c r="Z19" s="35">
         <v>2.5</v>
@@ -3663,27 +3643,21 @@
       </c>
       <c r="E23" s="46">
         <f>IF(E18=FALSE,0,E15*$P$18*0.08*0.08+(E14-E15)*$P$19*0.12*0.12)</f>
-        <v>680.22504000000004</v>
       </c>
       <c r="F23" s="46">
         <f>IF(F18=FALSE,0,F15*$P$18*0.08*0.08+(F14-F15)*$P$19*0.12*0.12)</f>
-        <v>680.22504000000004</v>
       </c>
       <c r="G23" s="63">
         <f t="shared" ref="G23:J23" si="3">F23*1.01</f>
-        <v>687.02729040000008</v>
       </c>
       <c r="H23" s="63">
         <f t="shared" si="3"/>
-        <v>693.89756330400007</v>
       </c>
       <c r="I23" s="63">
         <f t="shared" si="3"/>
-        <v>700.83653893704013</v>
       </c>
       <c r="J23" s="63">
         <f t="shared" si="3"/>
-        <v>707.84490432641053</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
@@ -3716,32 +3690,28 @@
       </c>
       <c r="E24" s="46">
         <f t="shared" ref="E24:J24" si="4">IF(E19=FALSE,0,$H$10*0.8*0.45)</f>
-        <v>144</v>
       </c>
       <c r="F24" s="63">
         <f t="shared" si="4"/>
-        <v>144</v>
       </c>
       <c r="G24" s="63">
         <f t="shared" si="4"/>
-        <v>144</v>
       </c>
       <c r="H24" s="63">
         <f t="shared" si="4"/>
-        <v>144</v>
       </c>
       <c r="I24" s="63">
         <f t="shared" si="4"/>
-        <v>144</v>
       </c>
       <c r="J24" s="63">
         <f t="shared" si="4"/>
-        <v>144</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
-      <c r="N24" s="69" t="s">
-        <v>177</v>
+      <c r="N24" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サンクスLINE誘導はオプション（このプランのSIMには入れていない）</t>
+        </is>
       </c>
       <c r="O24" s="22" t="s">
         <v>44</v>
@@ -3769,27 +3739,21 @@
       </c>
       <c r="E25" s="46">
         <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
-        <v>0</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" ref="F25:J25" si="5">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
-        <v>0</v>
       </c>
       <c r="G25" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
       </c>
       <c r="I25" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
       </c>
       <c r="J25" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="7"/>
@@ -3817,27 +3781,21 @@
       </c>
       <c r="E26" s="46">
         <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
-        <v>1253.66004</v>
       </c>
       <c r="F26" s="46">
         <f t="shared" ref="F26:J26" si="6">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
-        <v>1253.66004</v>
       </c>
       <c r="G26" s="46">
         <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
-        <v>1260.4622904</v>
       </c>
       <c r="H26" s="46">
         <f t="shared" si="6"/>
-        <v>1267.3325633040001</v>
       </c>
       <c r="I26" s="46">
         <f t="shared" si="6"/>
-        <v>1274.2715389370401</v>
       </c>
       <c r="J26" s="46">
         <f t="shared" si="6"/>
-        <v>1281.2799043264106</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
@@ -3870,23 +3828,18 @@
       </c>
       <c r="F27" s="47">
         <f>ROUND(E27*1.02,3)</f>
-        <v>0.34799999999999998</v>
       </c>
       <c r="G27" s="47">
         <f>ROUND(F27*1.02,3)</f>
-        <v>0.35499999999999998</v>
       </c>
       <c r="H27" s="47">
         <f>ROUND(G27*1.02,3)</f>
-        <v>0.36199999999999999</v>
       </c>
       <c r="I27" s="47">
         <f>ROUND(H27*1.02,3)</f>
-        <v>0.36899999999999999</v>
       </c>
       <c r="J27" s="47">
         <f>ROUND(I27*1.02,3)</f>
-        <v>0.376</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
@@ -3919,27 +3872,21 @@
       </c>
       <c r="E28" s="49">
         <f>+D28+E26</f>
-        <v>81157.660040000002</v>
       </c>
       <c r="F28" s="49">
         <f t="shared" ref="F28:J28" si="7">+E28+F26</f>
-        <v>82411.320080000005</v>
       </c>
       <c r="G28" s="49">
         <f t="shared" si="7"/>
-        <v>83671.782370400004</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="7"/>
-        <v>84939.114933703997</v>
       </c>
       <c r="I28" s="49">
         <f t="shared" si="7"/>
-        <v>86213.386472641039</v>
       </c>
       <c r="J28" s="49">
         <f t="shared" si="7"/>
-        <v>87494.666376967449</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
@@ -3969,31 +3916,24 @@
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
-        <v>52656.736000000004</v>
       </c>
       <c r="E29" s="50">
         <f>+E28*(1-E27)</f>
-        <v>53482.897966360004</v>
       </c>
       <c r="F29" s="50">
         <f t="shared" ref="F29:J29" si="8">+F28*(1-F27)</f>
-        <v>53732.180692160007</v>
       </c>
       <c r="G29" s="50">
         <f t="shared" si="8"/>
-        <v>53968.299628908004</v>
       </c>
       <c r="H29" s="50">
         <f t="shared" si="8"/>
-        <v>54191.155327703149</v>
       </c>
       <c r="I29" s="50">
         <f t="shared" si="8"/>
-        <v>54400.6468642365</v>
       </c>
       <c r="J29" s="50">
         <f t="shared" si="8"/>
-        <v>54596.671819227689</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -4056,31 +3996,24 @@
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
-        <v>6044.9932928000007</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>14658.567002828933</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>14726.890292660493</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>14791.605657507293</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>11882.148672369864</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>11928.082544191562</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>11971.063684649169</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -4130,7 +4063,6 @@
       </c>
       <c r="Q32" s="73">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
-        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
@@ -4148,27 +4080,21 @@
       </c>
       <c r="E33" s="63">
         <f t="shared" ref="E33:J33" si="9">+(E26-E24)*E32*$P$26*$P$27*$P$36</f>
-        <v>706.72417008534012</v>
       </c>
       <c r="F33" s="63">
         <f t="shared" si="9"/>
-        <v>706.72417008534012</v>
       </c>
       <c r="G33" s="63">
         <f t="shared" si="9"/>
-        <v>711.05641112796854</v>
       </c>
       <c r="H33" s="63">
         <f t="shared" si="9"/>
-        <v>715.43197458102338</v>
       </c>
       <c r="I33" s="63">
         <f t="shared" si="9"/>
-        <v>719.85129366860861</v>
       </c>
       <c r="J33" s="63">
         <f t="shared" si="9"/>
-        <v>724.31480594706977</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -4180,7 +4106,6 @@
       </c>
       <c r="Q33" s="73">
         <f t="shared" ref="Q33:Q35" si="10">+IF(P33=TRUE,1.1,0.95)</f>
-        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
@@ -4191,31 +4116,24 @@
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
-        <v>210626.94400000002</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E26*E32</f>
-        <v>134627.25531926402</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F26*F32</f>
-        <v>135225.53386118403</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G26*G32</f>
-        <v>135826.23056137923</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H26*H32</f>
-        <v>110383.68104571004</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I26*I32</f>
-        <v>110820.59967401929</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J26*J32</f>
-        <v>111232.00941454922</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -4227,7 +4145,6 @@
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="10"/>
-        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
@@ -4238,31 +4155,24 @@
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
-        <v>6165.8931586560011</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
-        <v>31498.84690447426</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" ref="F35:J35" si="11">+F31+F33+1.05*(F31+F33)</f>
-        <v>31638.909648628964</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="11"/>
-        <v>31780.457240702286</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="11"/>
-        <v>25825.040326249316</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="11"/>
-        <v>25928.264367613352</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="11"/>
-        <v>26025.52590572229</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -4274,16 +4184,14 @@
       </c>
       <c r="Q35" s="73">
         <f t="shared" si="10"/>
-        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="6" t="str">
+      <c r="B36" s="6">
         <f>+C8</f>
-        <v>応募</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="11">
@@ -4291,31 +4199,24 @@
       </c>
       <c r="E36" s="111">
         <f>ROUND(E35*0.004,0)</f>
-        <v>126</v>
       </c>
       <c r="F36" s="111">
         <f>ROUND(F35*0.0045,0)</f>
-        <v>142</v>
       </c>
       <c r="G36" s="111">
         <f>ROUND(G35*0.0055,0)</f>
-        <v>175</v>
       </c>
       <c r="H36" s="111">
         <f>ROUND(H35*0.0065,0)</f>
-        <v>168</v>
       </c>
       <c r="I36" s="111">
         <f>ROUND(I35*0.0075,0)</f>
-        <v>194</v>
       </c>
       <c r="J36" s="111">
         <f>ROUND(J35*0.009,0)</f>
-        <v>234</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
-        <v>1039</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
@@ -4326,15 +4227,13 @@
       </c>
       <c r="P36" s="74">
         <f>1*(Q32*Q33*Q34*Q35)</f>
-        <v>1.4641000000000006</v>
       </c>
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="146"/>
-      <c r="B37" s="6" t="str">
+      <c r="B37" s="6">
         <f>+C9</f>
-        <v>-</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
@@ -4360,7 +4259,6 @@
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
-        <v>0</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
@@ -4371,9 +4269,8 @@
       <c r="A38" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6" t="str">
+      <c r="B38" s="6">
         <f>+C10</f>
-        <v>-</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="11">
@@ -4399,7 +4296,6 @@
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
-        <v>0</v>
       </c>
       <c r="L38" s="7"/>
       <c r="N38" s="69" t="s">
@@ -4411,9 +4307,8 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="146"/>
-      <c r="B39" s="6" t="str">
+      <c r="B39" s="6">
         <f>+C11</f>
-        <v>-</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="11">
@@ -4439,7 +4334,6 @@
       </c>
       <c r="K39" s="115">
         <f>SUM(E39:J39)</f>
-        <v>0</v>
       </c>
       <c r="L39" s="7"/>
       <c r="N39" s="69" t="s">
@@ -4457,35 +4351,27 @@
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="12">+SUM(D36:D39)</f>
-        <v>0</v>
       </c>
       <c r="E40" s="10">
         <f t="shared" si="12"/>
-        <v>126</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="12"/>
-        <v>142</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="12"/>
-        <v>175</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="12"/>
-        <v>168</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="12"/>
-        <v>194</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="12"/>
-        <v>234</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
-        <v>1039</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -4496,31 +4382,24 @@
       </c>
       <c r="D41" s="18">
         <f t="shared" ref="D41" si="13">+IFERROR(D40/D35,0)</f>
-        <v>0</v>
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
-        <v>4.0001464301889196E-3</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="14">+IFERROR(F40/F35,0)</f>
-        <v>4.4881445529256223E-3</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="14"/>
-        <v>5.5065287033023453E-3</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="14"/>
-        <v>6.5053141399837406E-3</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="14"/>
-        <v>7.4821822721895265E-3</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="14"/>
-        <v>8.9911727758227502E-3</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>118</v>
@@ -4558,27 +4437,21 @@
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
-        <v>313881.76595779206</v>
       </c>
       <c r="F44" s="31">
         <f t="shared" ref="F44:J44" si="15">+F75*F76</f>
-        <v>315676.60158355208</v>
       </c>
       <c r="G44" s="31">
         <f t="shared" si="15"/>
-        <v>317478.69168413768</v>
       </c>
       <c r="H44" s="31">
         <f t="shared" si="15"/>
-        <v>241151.04313713009</v>
       </c>
       <c r="I44" s="31">
         <f t="shared" si="15"/>
-        <v>242461.79902205788</v>
       </c>
       <c r="J44" s="31">
         <f t="shared" si="15"/>
-        <v>243696.02824364766</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
@@ -4590,35 +4463,27 @@
       <c r="B45" s="138"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
-        <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
-        <v>365000</v>
       </c>
       <c r="E45" s="27">
         <f t="shared" ref="E45:J45" si="16">SUM(E65:E68)+SUM(E71:E72)</f>
-        <v>75000</v>
       </c>
       <c r="F45" s="27">
         <f t="shared" si="16"/>
-        <v>75000</v>
       </c>
       <c r="G45" s="27">
         <f t="shared" si="16"/>
-        <v>75000</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="16"/>
-        <v>75000</v>
       </c>
       <c r="I45" s="27">
         <f t="shared" si="16"/>
-        <v>75000</v>
       </c>
       <c r="J45" s="27">
         <f t="shared" si="16"/>
-        <v>75000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
@@ -4637,27 +4502,21 @@
       </c>
       <c r="E46" s="28">
         <f t="shared" ref="E46:J46" si="17">+SUM(E65:E67)/(E28-D28)</f>
-        <v>47.859864784395519</v>
       </c>
       <c r="F46" s="28">
         <f t="shared" si="17"/>
-        <v>47.859864784395519</v>
       </c>
       <c r="G46" s="28">
         <f t="shared" si="17"/>
-        <v>47.601582734346948</v>
       </c>
       <c r="H46" s="28">
         <f t="shared" si="17"/>
-        <v>47.343532185093785</v>
       </c>
       <c r="I46" s="28">
         <f t="shared" si="17"/>
-        <v>47.085725582516055</v>
       </c>
       <c r="J46" s="28">
         <f t="shared" si="17"/>
-        <v>46.828175324846775</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
@@ -4673,27 +4532,21 @@
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="18">+E51/E35</f>
-        <v>12.345904824298609</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="18"/>
-        <v>12.347979305300795</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="18"/>
-        <v>12.349686749675747</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="18"/>
-        <v>12.242034829110608</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="18"/>
-        <v>12.243850746083691</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
-        <v>12.245517320115912</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
@@ -4709,27 +4562,21 @@
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="19">+SUM(E36:E39)/E35</f>
-        <v>4.0001464301889196E-3</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="19"/>
-        <v>4.4881445529256223E-3</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="19"/>
-        <v>5.5065287033023453E-3</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="19"/>
-        <v>6.5053141399837406E-3</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="19"/>
-        <v>7.4821822721895265E-3</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="19"/>
-        <v>8.9911727758227502E-3</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
@@ -4745,27 +4592,21 @@
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
-        <v>3086.3632218872385</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="20">+IFERROR(F51/SUM(F36:F39),0)</f>
-        <v>2751.2436731236062</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="20"/>
-        <v>2242.7353810522154</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="20"/>
-        <v>1881.8514472448219</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="20"/>
-        <v>1636.4010258868964</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="20"/>
-        <v>1361.9488386480668</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
@@ -4781,27 +4622,21 @@
       </c>
       <c r="E50" s="65">
         <f>+E36*$D$8+E38*$D$10</f>
-        <v>0</v>
       </c>
       <c r="F50" s="65">
         <f t="shared" ref="F50:J50" si="21">+F36*$D$8+F38*$D$10</f>
-        <v>0</v>
       </c>
       <c r="G50" s="65">
         <f t="shared" si="21"/>
-        <v>0</v>
       </c>
       <c r="H50" s="65">
         <f t="shared" si="21"/>
-        <v>0</v>
       </c>
       <c r="I50" s="65">
         <f t="shared" si="21"/>
-        <v>0</v>
       </c>
       <c r="J50" s="65">
         <f t="shared" si="21"/>
-        <v>0</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
@@ -4813,35 +4648,27 @@
       <c r="B51" s="136"/>
       <c r="C51" s="110">
         <f>+C45</f>
-        <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
-        <v>365000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
-        <v>388881.76595779206</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="22">SUM(F45,F50)+F44</f>
-        <v>390676.60158355208</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="22"/>
-        <v>392478.69168413768</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="22"/>
-        <v>316151.04313713009</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="22"/>
-        <v>317461.79902205791</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
-        <v>318696.02824364766</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -4871,31 +4698,24 @@
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
-        <v>541880.83200000005</v>
       </c>
       <c r="E54" s="28">
         <f t="shared" ref="E54:J54" si="23">+E75*E76</f>
-        <v>313881.76595779206</v>
       </c>
       <c r="F54" s="28">
         <f t="shared" si="23"/>
-        <v>315676.60158355208</v>
       </c>
       <c r="G54" s="28">
         <f t="shared" si="23"/>
-        <v>317478.69168413768</v>
       </c>
       <c r="H54" s="28">
         <f t="shared" si="23"/>
-        <v>241151.04313713009</v>
       </c>
       <c r="I54" s="28">
         <f t="shared" si="23"/>
-        <v>242461.79902205788</v>
       </c>
       <c r="J54" s="28">
         <f t="shared" si="23"/>
-        <v>243696.02824364766</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
@@ -4911,31 +4731,24 @@
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
-        <v>365000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
-        <v>688881.76595779206</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="24">SUM(F65:F72)+F54</f>
-        <v>690676.60158355208</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="24"/>
-        <v>692478.69168413768</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="24"/>
-        <v>616151.04313713009</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="24"/>
-        <v>617461.79902205791</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="24"/>
-        <v>618696.02824364766</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
@@ -4951,27 +4764,21 @@
       </c>
       <c r="E56" s="28">
         <f>+SUM(E65:E67)/(E28-D28)</f>
-        <v>47.859864784395519</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" ref="F56:J56" si="25">+SUM(F65:F67)/(F28-E28)</f>
-        <v>47.859864784395519</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="25"/>
-        <v>47.601582734346948</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="25"/>
-        <v>47.343532185093785</v>
       </c>
       <c r="I56" s="28">
         <f t="shared" si="25"/>
-        <v>47.085725582516055</v>
       </c>
       <c r="J56" s="28">
         <f t="shared" si="25"/>
-        <v>46.828175324846775</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
@@ -4987,27 +4794,21 @@
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
-        <v>21.870062991415082</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="26">+F61/F35</f>
-        <v>21.829974839650703</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="26"/>
-        <v>21.789450241051195</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="26"/>
-        <v>23.858667221938717</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="26"/>
-        <v>23.814235703077802</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="26"/>
-        <v>23.772661904504055</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
@@ -5023,27 +4824,21 @@
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="27">+SUM(E36:E39)/E35</f>
-        <v>4.0001464301889196E-3</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="27"/>
-        <v>4.4881445529256223E-3</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="27"/>
-        <v>5.5065287033023453E-3</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="27"/>
-        <v>6.5053141399837406E-3</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="27"/>
-        <v>7.4821822721895265E-3</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="27"/>
-        <v>8.9911727758227502E-3</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
@@ -5057,27 +4852,21 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
-        <v>5467.3156028396197</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="28">+IFERROR(F55/F40,0)</f>
-        <v>4863.9197294616342</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="28"/>
-        <v>3957.0210953379296</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="28"/>
-        <v>3667.5657329591077</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="28"/>
-        <v>3182.7927784642161</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="28"/>
-        <v>2644.0001206993488</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
@@ -5106,31 +4895,24 @@
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
-        <v>365000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
-        <v>688881.76595779206</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="29">+SUM(F65:F72)+F54</f>
-        <v>690676.60158355208</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="29"/>
-        <v>692478.69168413768</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="29"/>
-        <v>616151.04313713009</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="29"/>
-        <v>617461.79902205791</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="29"/>
-        <v>618696.02824364766</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -5219,28 +5001,30 @@
         <v>0</v>
       </c>
       <c r="D67" s="51">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="E67" s="28">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="F67" s="28">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="G67" s="28">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H67" s="28">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="I67" s="28">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="J67" s="28">
-        <v>30000</v>
-      </c>
-      <c r="N67" s="69" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="N67" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サンクスLINE誘導：オプション（初期15万円・月3万円〜）</t>
+        </is>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5256,27 +5040,21 @@
       </c>
       <c r="E68" s="28">
         <f t="shared" ref="E68:J68" si="30">IF(E34&lt;5000,5000,15000)</f>
-        <v>15000</v>
       </c>
       <c r="F68" s="28">
         <f t="shared" si="30"/>
-        <v>15000</v>
       </c>
       <c r="G68" s="28">
         <f t="shared" si="30"/>
-        <v>15000</v>
       </c>
       <c r="H68" s="28">
         <f t="shared" si="30"/>
-        <v>15000</v>
       </c>
       <c r="I68" s="28">
         <f t="shared" si="30"/>
-        <v>15000</v>
       </c>
       <c r="J68" s="28">
         <f t="shared" si="30"/>
-        <v>15000</v>
       </c>
       <c r="N68" s="69" t="s">
         <v>190</v>
@@ -5430,31 +5208,24 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
-        <v>365000</v>
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="31">SUM(E65:E72)+E54</f>
-        <v>688881.76595779206</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="31"/>
-        <v>690676.60158355208</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="31"/>
-        <v>692478.69168413768</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="31"/>
-        <v>616151.04313713009</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="31"/>
-        <v>617461.79902205791</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="31"/>
-        <v>618696.02824364766</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5475,31 +5246,24 @@
       </c>
       <c r="D75" s="41">
         <f t="shared" ref="D75:J75" si="32">+IF(D34&lt;30001,0,D34-30000)</f>
-        <v>180626.94400000002</v>
       </c>
       <c r="E75" s="41">
         <f t="shared" si="32"/>
-        <v>104627.25531926402</v>
       </c>
       <c r="F75" s="41">
         <f t="shared" si="32"/>
-        <v>105225.53386118403</v>
       </c>
       <c r="G75" s="41">
         <f t="shared" si="32"/>
-        <v>105826.23056137923</v>
       </c>
       <c r="H75" s="41">
         <f t="shared" si="32"/>
-        <v>80383.681045710036</v>
       </c>
       <c r="I75" s="41">
         <f t="shared" si="32"/>
-        <v>80820.599674019293</v>
       </c>
       <c r="J75" s="41">
         <f t="shared" si="32"/>
-        <v>81232.009414549218</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5508,31 +5272,24 @@
       </c>
       <c r="D76" s="5">
         <f t="shared" ref="D76:J76" si="33">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="E76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
       <c r="F76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
       <c r="G76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
       <c r="H76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
       <c r="J76" s="5">
         <f t="shared" si="33"/>
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5622,17 +5379,14 @@
         <v>140</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="86" t="str">
+      <c r="C4" s="86">
         <f>+SIM①_月3投稿!D24</f>
-        <v>--</v>
       </c>
       <c r="D4" s="28">
         <f>+SIM①_月3投稿!G51</f>
-        <v>392478.69168413768</v>
       </c>
       <c r="E4" s="28">
         <f>+SIM①_月3投稿!J51</f>
-        <v>318696.02824364766</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -5641,17 +5395,14 @@
         <v>141</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="86" t="str">
+      <c r="C5" s="86">
         <f>+SIM①_月3投稿!D25</f>
-        <v>--</v>
       </c>
       <c r="D5" s="28">
         <f>+SIM①_月3投稿!G61</f>
-        <v>692478.69168413768</v>
       </c>
       <c r="E5" s="28">
         <f>+SIM①_月3投稿!J61</f>
-        <v>618696.02824364766</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -5662,15 +5413,12 @@
       <c r="B6" s="7"/>
       <c r="C6" s="117">
         <f>+SIM①_月3投稿!D28</f>
-        <v>79904</v>
       </c>
       <c r="D6" s="87">
         <f>+SIM①_月3投稿!G28</f>
-        <v>83671.782370400004</v>
       </c>
       <c r="E6" s="87">
         <f>+SIM①_月3投稿!J28</f>
-        <v>87494.666376967449</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -5681,15 +5429,12 @@
       <c r="B7" s="7"/>
       <c r="C7" s="88">
         <f>+SIM①_月3投稿!D27</f>
-        <v>0.34100000000000003</v>
       </c>
       <c r="D7" s="89">
         <f>+SIM①_月3投稿!G27</f>
-        <v>0.35499999999999998</v>
       </c>
       <c r="E7" s="89">
         <f>+SIM①_月3投稿!J27</f>
-        <v>0.376</v>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -5700,15 +5445,12 @@
       <c r="B8" s="7"/>
       <c r="C8" s="117">
         <f>+SIM①_月3投稿!D29</f>
-        <v>52656.736000000004</v>
       </c>
       <c r="D8" s="10">
         <f>+SIM①_月3投稿!G29</f>
-        <v>53968.299628908004</v>
       </c>
       <c r="E8" s="10">
         <f>+SIM①_月3投稿!J29</f>
-        <v>54596.671819227689</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -5727,15 +5469,12 @@
       <c r="B10" s="7"/>
       <c r="C10" s="117">
         <f>+SIM①_月3投稿!D34</f>
-        <v>210626.94400000002</v>
       </c>
       <c r="D10" s="10">
         <f>+SIM①_月3投稿!G34</f>
-        <v>135826.23056137923</v>
       </c>
       <c r="E10" s="10">
         <f>+SIM①_月3投稿!J34</f>
-        <v>111232.00941454922</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -5746,15 +5485,12 @@
       <c r="B11" s="7"/>
       <c r="C11" s="117">
         <f>+SIM①_月3投稿!D35</f>
-        <v>6165.8931586560011</v>
       </c>
       <c r="D11" s="10">
         <f>+SIM①_月3投稿!G35</f>
-        <v>31780.457240702286</v>
       </c>
       <c r="E11" s="10">
         <f>+SIM①_月3投稿!J35</f>
-        <v>26025.52590572229</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -5765,15 +5501,12 @@
       <c r="B12" s="7"/>
       <c r="C12" s="28">
         <f>+IFERROR(C5/C11,0)</f>
-        <v>0</v>
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
-        <v>12.349686749675747</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
-        <v>12.245517320115912</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -5784,15 +5517,12 @@
       <c r="B13" s="7"/>
       <c r="C13" s="28">
         <f>+IFERROR(C6/C12,0)</f>
-        <v>0</v>
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
-        <v>21.789450241051195</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
-        <v>23.772661904504055</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -5814,15 +5544,12 @@
       <c r="B15" s="7"/>
       <c r="C15" s="87">
         <f>+SIM①_月3投稿!D16</f>
-        <v>400</v>
       </c>
       <c r="D15" s="87">
         <f>+SIM①_月3投稿!G16</f>
-        <v>400</v>
       </c>
       <c r="E15" s="87">
         <f>+SIM①_月3投稿!J16</f>
-        <v>400</v>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -5836,15 +5563,12 @@
       <c r="B16" s="7"/>
       <c r="C16" s="87">
         <f>+C17</f>
-        <v>0</v>
       </c>
       <c r="D16" s="87">
         <f>+D17</f>
-        <v>175</v>
       </c>
       <c r="E16" s="87">
         <f>+E17</f>
-        <v>234</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -5864,15 +5588,12 @@
       <c r="B17" s="7"/>
       <c r="C17" s="87">
         <f>+SIM①_月3投稿!D36</f>
-        <v>0</v>
       </c>
       <c r="D17" s="87">
         <f>+SIM①_月3投稿!G36</f>
-        <v>175</v>
       </c>
       <c r="E17" s="87">
         <f>+SIM①_月3投稿!J36</f>
-        <v>234</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -5904,15 +5625,12 @@
       <c r="B18" s="7"/>
       <c r="C18" s="87">
         <f>+SIM①_月3投稿!D37</f>
-        <v>0</v>
       </c>
       <c r="D18" s="87">
         <f>+SIM①_月3投稿!G37</f>
-        <v>0</v>
       </c>
       <c r="E18" s="87">
         <f>+SIM①_月3投稿!J37</f>
-        <v>0</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -5932,7 +5650,6 @@
       </c>
       <c r="X18" s="34">
         <f>+T18*2.5</f>
-        <v>37500000</v>
       </c>
       <c r="Y18" s="35">
         <v>2.5</v>
@@ -5945,15 +5662,12 @@
       <c r="B19" s="7"/>
       <c r="C19" s="87">
         <f>+SIM①_月3投稿!D38</f>
-        <v>0</v>
       </c>
       <c r="D19" s="87">
         <f>+SIM①_月3投稿!G38</f>
-        <v>0</v>
       </c>
       <c r="E19" s="87">
         <f>+SIM①_月3投稿!J38</f>
-        <v>0</v>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -5969,15 +5683,12 @@
       <c r="B20" s="7"/>
       <c r="C20" s="87">
         <f>+SIM①_月3投稿!D39</f>
-        <v>0</v>
       </c>
       <c r="D20" s="87">
         <f>+SIM①_月3投稿!G39</f>
-        <v>0</v>
       </c>
       <c r="E20" s="87">
         <f>+SIM①_月3投稿!J39</f>
-        <v>0</v>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -6004,17 +5715,14 @@
         <v>142</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="90" t="str">
+      <c r="C22" s="90">
         <f>+IFERROR(C4/C16,"--")</f>
-        <v>--</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
-        <v>2242.7353810522154</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
-        <v>1361.9488386480668</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -6028,17 +5736,14 @@
         <v>143</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="90" t="str">
+      <c r="C23" s="90">
         <f>+IFERROR(C5/C16,"--")</f>
-        <v>--</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
-        <v>3957.0210953379296</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
-        <v>2644.0001206993488</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -6067,15 +5772,12 @@
       <c r="B25" s="7"/>
       <c r="C25" s="10">
         <f>+SIM①_月3投稿!E68+C29*C30</f>
-        <v>556880.83200000005</v>
       </c>
       <c r="D25" s="10">
         <f>+SIM①_月3投稿!G68+D29*D30</f>
-        <v>332478.69168413768</v>
       </c>
       <c r="E25" s="10">
         <f>+SIM①_月3投稿!J68+E29*E30</f>
-        <v>258696.02824364766</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -6111,15 +5813,12 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
-        <v>180626.94400000002</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
-        <v>105826.23056137923</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
-        <v>81232.009414549218</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -6134,15 +5833,12 @@
       </c>
       <c r="C30" s="5">
         <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="E30" s="5">
         <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="R30" s="34"/>
       <c r="T30" s="34"/>

--- a/株式会社ワクトリ御中_LINEOA施策提案【SIM】ver1.0.xlsx
+++ b/株式会社ワクトリ御中_LINEOA施策提案【SIM】ver1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935E29B2-5ECE-4B1B-969E-7BB111D604E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E379D78-7BD1-4D8C-91BC-BD7AF55BE175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="SIM②_比較" sheetId="4" r:id="rId4"/>
     <sheet name="SIM考え方" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1" calcId="191029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1502,9 +1502,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>株式会社ワクトリ御中_LINEOA施策提案【SIM】プラン①（月3投稿）：ポップアップ＋サンクスLINE</t>
-  </si>
-  <si>
     <t>応募</t>
   </si>
   <si>
@@ -1614,6 +1611,10 @@
   </si>
   <si>
     <t>LINE運用コンサル：初期10万円〜（運用設計・構築）・月額27万円（ポップアップ3万円と合わせてプランの月額30万円）</t>
+  </si>
+  <si>
+    <t>株式会社ワクトリ御中_LINEOA施策提案【SIM】プラン①（月3投稿）：ポップアップ</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -2986,10 +2987,8 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">株式会社ワクトリ御中_LINEOA施策提案【SIM】プラン①（月3投稿）：ポップアップ</t>
-        </is>
+      <c r="A4" s="56" t="s">
+        <v>200</v>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -3060,7 +3059,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D8" s="33">
         <v>0</v>
@@ -3079,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="69" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O8" s="35" t="s">
         <v>158</v>
@@ -3129,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H10" s="125">
         <v>400</v>
@@ -3140,7 +3139,7 @@
       <c r="J10" s="29"/>
       <c r="K10" s="118"/>
       <c r="N10" s="132" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
@@ -3187,22 +3186,22 @@
         <v>29</v>
       </c>
       <c r="E13" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="G13" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="G13" s="36" t="s">
+      <c r="H13" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="H13" s="36" t="s">
+      <c r="I13" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="I13" s="36" t="s">
+      <c r="J13" s="36" t="s">
         <v>172</v>
-      </c>
-      <c r="J13" s="36" t="s">
-        <v>173</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>1</v>
@@ -3233,24 +3232,31 @@
       <c r="C14" s="99"/>
       <c r="D14" s="42">
         <f>+H8</f>
+        <v>85887</v>
       </c>
       <c r="E14" s="43">
         <f>+D14</f>
+        <v>85887</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" ref="F14:J14" si="0">+E14</f>
+        <v>85887</v>
       </c>
       <c r="G14" s="43">
         <f t="shared" si="0"/>
+        <v>85887</v>
       </c>
       <c r="H14" s="43">
         <f t="shared" si="0"/>
+        <v>85887</v>
       </c>
       <c r="I14" s="43">
         <f t="shared" si="0"/>
+        <v>85887</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="0"/>
+        <v>85887</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
@@ -3263,29 +3269,36 @@
       <c r="C15" s="99"/>
       <c r="D15" s="42">
         <f t="shared" ref="D15" si="1">+H9</f>
+        <v>0</v>
       </c>
       <c r="E15" s="43">
         <f t="shared" ref="E15:J16" si="2">+D15</f>
+        <v>0</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
       <c r="N15" s="69" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O15" s="17" t="s">
         <v>33</v>
@@ -3305,24 +3318,31 @@
       <c r="C16" s="99"/>
       <c r="D16" s="42">
         <f>H10</f>
+        <v>400</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="2"/>
+        <v>400</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -3418,7 +3438,7 @@
         <v>22</v>
       </c>
       <c r="N18" s="69" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O18" s="22" t="s">
         <v>39</v>
@@ -3503,6 +3523,7 @@
       </c>
       <c r="Y19" s="34">
         <f>+U19*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Z19" s="35">
         <v>2.5</v>
@@ -3618,7 +3639,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="7"/>
       <c r="N22" s="69" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O22" s="17" t="s">
         <v>41</v>
@@ -3643,21 +3664,27 @@
       </c>
       <c r="E23" s="46">
         <f>IF(E18=FALSE,0,E15*$P$18*0.08*0.08+(E14-E15)*$P$19*0.12*0.12)</f>
+        <v>680.22504000000004</v>
       </c>
       <c r="F23" s="46">
         <f>IF(F18=FALSE,0,F15*$P$18*0.08*0.08+(F14-F15)*$P$19*0.12*0.12)</f>
+        <v>680.22504000000004</v>
       </c>
       <c r="G23" s="63">
         <f t="shared" ref="G23:J23" si="3">F23*1.01</f>
+        <v>687.02729040000008</v>
       </c>
       <c r="H23" s="63">
         <f t="shared" si="3"/>
+        <v>693.89756330400007</v>
       </c>
       <c r="I23" s="63">
         <f t="shared" si="3"/>
+        <v>700.83653893704013</v>
       </c>
       <c r="J23" s="63">
         <f t="shared" si="3"/>
+        <v>707.84490432641053</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
@@ -3690,28 +3717,32 @@
       </c>
       <c r="E24" s="46">
         <f t="shared" ref="E24:J24" si="4">IF(E19=FALSE,0,$H$10*0.8*0.45)</f>
+        <v>0</v>
       </c>
       <c r="F24" s="63">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="G24" s="63">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="H24" s="63">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="I24" s="63">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="J24" s="63">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
-      <c r="N24" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サンクスLINE誘導はオプション（このプランのSIMには入れていない）</t>
-        </is>
+      <c r="N24" s="69" t="s">
+        <v>176</v>
       </c>
       <c r="O24" s="22" t="s">
         <v>44</v>
@@ -3739,21 +3770,27 @@
       </c>
       <c r="E25" s="46">
         <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" ref="F25:J25" si="5">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="G25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="I25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="J25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="7"/>
@@ -3781,26 +3818,32 @@
       </c>
       <c r="E26" s="46">
         <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
+        <v>1109.66004</v>
       </c>
       <c r="F26" s="46">
         <f t="shared" ref="F26:J26" si="6">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>1109.66004</v>
       </c>
       <c r="G26" s="46">
         <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>1116.4622904</v>
       </c>
       <c r="H26" s="46">
         <f t="shared" si="6"/>
+        <v>1123.3325633040001</v>
       </c>
       <c r="I26" s="46">
         <f t="shared" si="6"/>
+        <v>1130.2715389370401</v>
       </c>
       <c r="J26" s="46">
         <f t="shared" si="6"/>
+        <v>1137.2799043264106</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
       <c r="N26" s="72" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O26" s="17" t="s">
         <v>41</v>
@@ -3828,23 +3871,28 @@
       </c>
       <c r="F27" s="47">
         <f>ROUND(E27*1.02,3)</f>
+        <v>0.34799999999999998</v>
       </c>
       <c r="G27" s="47">
         <f>ROUND(F27*1.02,3)</f>
+        <v>0.35499999999999998</v>
       </c>
       <c r="H27" s="47">
         <f>ROUND(G27*1.02,3)</f>
+        <v>0.36199999999999999</v>
       </c>
       <c r="I27" s="47">
         <f>ROUND(H27*1.02,3)</f>
+        <v>0.36899999999999999</v>
       </c>
       <c r="J27" s="47">
         <f>ROUND(I27*1.02,3)</f>
+        <v>0.376</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
       <c r="N27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O27" s="17" t="s">
         <v>42</v>
@@ -3872,26 +3920,32 @@
       </c>
       <c r="E28" s="49">
         <f>+D28+E26</f>
+        <v>81013.660040000002</v>
       </c>
       <c r="F28" s="49">
         <f t="shared" ref="F28:J28" si="7">+E28+F26</f>
+        <v>82123.320080000005</v>
       </c>
       <c r="G28" s="49">
         <f t="shared" si="7"/>
+        <v>83239.782370400004</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="7"/>
+        <v>84363.114933703997</v>
       </c>
       <c r="I28" s="49">
         <f t="shared" si="7"/>
+        <v>85493.386472641039</v>
       </c>
       <c r="J28" s="49">
         <f t="shared" si="7"/>
+        <v>86630.666376967449</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
       <c r="N28" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O28" s="22" t="s">
         <v>44</v>
@@ -3916,24 +3970,31 @@
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
+        <v>52656.736000000004</v>
       </c>
       <c r="E29" s="50">
         <f>+E28*(1-E27)</f>
+        <v>53388.001966360003</v>
       </c>
       <c r="F29" s="50">
         <f t="shared" ref="F29:J29" si="8">+F28*(1-F27)</f>
+        <v>53544.404692160002</v>
       </c>
       <c r="G29" s="50">
         <f t="shared" si="8"/>
+        <v>53689.659628908004</v>
       </c>
       <c r="H29" s="50">
         <f t="shared" si="8"/>
+        <v>53823.667327703151</v>
       </c>
       <c r="I29" s="50">
         <f t="shared" si="8"/>
+        <v>53946.326864236493</v>
       </c>
       <c r="J29" s="50">
         <f t="shared" si="8"/>
+        <v>54057.535819227691</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -3976,7 +4037,7 @@
       <c r="K30" s="11"/>
       <c r="L30" s="7"/>
       <c r="N30" s="69" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O30" s="17" t="s">
         <v>122</v>
@@ -3996,24 +4057,31 @@
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
+        <v>6044.9932928000007</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>14632.557952699013</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>14675.42473671297</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>14715.236140054492</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>11801.571924653257</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>11828.466698170443</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>11852.850775773393</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -4053,7 +4121,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
       <c r="N32" s="69" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O32" s="17" t="s">
         <v>126</v>
@@ -4063,6 +4131,7 @@
       </c>
       <c r="Q32" s="73">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
@@ -4080,21 +4149,27 @@
       </c>
       <c r="E33" s="63">
         <f t="shared" ref="E33:J33" si="9">+(E26-E24)*E32*$P$26*$P$27*$P$36</f>
+        <v>706.72417008534012</v>
       </c>
       <c r="F33" s="63">
         <f t="shared" si="9"/>
+        <v>706.72417008534012</v>
       </c>
       <c r="G33" s="63">
         <f t="shared" si="9"/>
+        <v>711.05641112796854</v>
       </c>
       <c r="H33" s="63">
         <f t="shared" si="9"/>
+        <v>715.43197458102338</v>
       </c>
       <c r="I33" s="63">
         <f t="shared" si="9"/>
+        <v>719.85129366860861</v>
       </c>
       <c r="J33" s="63">
         <f t="shared" si="9"/>
+        <v>724.31480594706977</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -4106,6 +4181,7 @@
       </c>
       <c r="Q33" s="73">
         <f t="shared" ref="Q33:Q35" si="10">+IF(P33=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
@@ -4116,24 +4192,31 @@
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
+        <v>210626.94400000002</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E26*E32</f>
+        <v>133679.50491926403</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F26*F32</f>
+        <v>134054.87146118403</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G26*G32</f>
+        <v>134437.49456137922</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H26*H32</f>
+        <v>108958.10408571005</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I26*I32</f>
+        <v>109228.30527401928</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J26*J32</f>
+        <v>109476.86829454922</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -4145,6 +4228,7 @@
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="10"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
@@ -4155,24 +4239,31 @@
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
+        <v>6165.8931586560011</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
+        <v>31445.528351707922</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" ref="F35:J35" si="11">+F31+F33+1.05*(F31+F33)</f>
+        <v>31533.405258936535</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="11"/>
+        <v>31623.899729924047</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="11"/>
+        <v>25659.857993430276</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="11"/>
+        <v>25724.051883270058</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="11"/>
+        <v>25783.189442526949</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -4184,14 +4275,16 @@
       </c>
       <c r="Q35" s="73">
         <f t="shared" si="10"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="6" t="str">
         <f>+C8</f>
+        <v>応募</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="11">
@@ -4199,41 +4292,50 @@
       </c>
       <c r="E36" s="111">
         <f>ROUND(E35*0.004,0)</f>
+        <v>126</v>
       </c>
       <c r="F36" s="111">
         <f>ROUND(F35*0.0045,0)</f>
+        <v>142</v>
       </c>
       <c r="G36" s="111">
         <f>ROUND(G35*0.0055,0)</f>
+        <v>174</v>
       </c>
       <c r="H36" s="111">
         <f>ROUND(H35*0.0065,0)</f>
+        <v>167</v>
       </c>
       <c r="I36" s="111">
         <f>ROUND(I35*0.0075,0)</f>
+        <v>193</v>
       </c>
       <c r="J36" s="111">
         <f>ROUND(J35*0.009,0)</f>
+        <v>232</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
+        <v>1034</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O36" s="17" t="s">
         <v>127</v>
       </c>
       <c r="P36" s="74">
         <f>1*(Q32*Q33*Q34*Q35)</f>
+        <v>1.4641000000000006</v>
       </c>
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="146"/>
-      <c r="B37" s="6">
+      <c r="B37" s="6" t="str">
         <f>+C9</f>
+        <v>-</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
@@ -4259,6 +4361,7 @@
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
+        <v>0</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
@@ -4269,8 +4372,9 @@
       <c r="A38" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="6" t="str">
         <f>+C10</f>
+        <v>-</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="11">
@@ -4296,6 +4400,7 @@
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
+        <v>0</v>
       </c>
       <c r="L38" s="7"/>
       <c r="N38" s="69" t="s">
@@ -4307,8 +4412,9 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="146"/>
-      <c r="B39" s="6">
+      <c r="B39" s="6" t="str">
         <f>+C11</f>
+        <v>-</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="11">
@@ -4334,6 +4440,7 @@
       </c>
       <c r="K39" s="115">
         <f>SUM(E39:J39)</f>
+        <v>0</v>
       </c>
       <c r="L39" s="7"/>
       <c r="N39" s="69" t="s">
@@ -4351,27 +4458,35 @@
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="12">+SUM(D36:D39)</f>
+        <v>0</v>
       </c>
       <c r="E40" s="10">
         <f t="shared" si="12"/>
+        <v>126</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="12"/>
+        <v>142</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="12"/>
+        <v>174</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="12"/>
+        <v>167</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="12"/>
+        <v>193</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="12"/>
+        <v>232</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
+        <v>1034</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -4382,24 +4497,31 @@
       </c>
       <c r="D41" s="18">
         <f t="shared" ref="D41" si="13">+IFERROR(D40/D35,0)</f>
+        <v>0</v>
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
+        <v>4.0069290167661148E-3</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="14">+IFERROR(F40/F35,0)</f>
+        <v>4.5031609759227428E-3</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="14"/>
+        <v>5.5021677113197042E-3</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="14"/>
+        <v>6.508219961418228E-3</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="14"/>
+        <v>7.5027060618517811E-3</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="14"/>
+        <v>8.9981109791381284E-3</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>118</v>
@@ -4437,21 +4559,27 @@
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
+        <v>311038.51475779212</v>
       </c>
       <c r="F44" s="31">
         <f t="shared" ref="F44:J44" si="15">+F75*F76</f>
+        <v>312164.61438355211</v>
       </c>
       <c r="G44" s="31">
         <f t="shared" si="15"/>
+        <v>313312.4836841377</v>
       </c>
       <c r="H44" s="31">
         <f t="shared" si="15"/>
+        <v>236874.31225713014</v>
       </c>
       <c r="I44" s="31">
         <f t="shared" si="15"/>
+        <v>237684.91582205784</v>
       </c>
       <c r="J44" s="31">
         <f t="shared" si="15"/>
+        <v>238430.60488364764</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
@@ -4463,32 +4591,40 @@
       <c r="B45" s="138"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
+        <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
+        <v>215000</v>
       </c>
       <c r="E45" s="27">
         <f t="shared" ref="E45:J45" si="16">SUM(E65:E68)+SUM(E71:E72)</f>
+        <v>45000</v>
       </c>
       <c r="F45" s="27">
         <f t="shared" si="16"/>
+        <v>45000</v>
       </c>
       <c r="G45" s="27">
         <f t="shared" si="16"/>
+        <v>45000</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="16"/>
+        <v>45000</v>
       </c>
       <c r="I45" s="27">
         <f t="shared" si="16"/>
+        <v>45000</v>
       </c>
       <c r="J45" s="27">
         <f t="shared" si="16"/>
+        <v>45000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
       <c r="N45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -4502,21 +4638,27 @@
       </c>
       <c r="E46" s="28">
         <f t="shared" ref="E46:J46" si="17">+SUM(E65:E67)/(E28-D28)</f>
+        <v>27.035307137850914</v>
       </c>
       <c r="F46" s="28">
         <f t="shared" si="17"/>
+        <v>27.035307137850914</v>
       </c>
       <c r="G46" s="28">
         <f t="shared" si="17"/>
+        <v>26.870589591746796</v>
       </c>
       <c r="H46" s="28">
         <f t="shared" si="17"/>
+        <v>26.70624976076785</v>
       </c>
       <c r="I46" s="28">
         <f t="shared" si="17"/>
+        <v>26.542294454493064</v>
       </c>
       <c r="J46" s="28">
         <f t="shared" si="17"/>
+        <v>26.378730412693315</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
@@ -4532,21 +4674,27 @@
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="18">+E51/E35</f>
+        <v>11.322389332296092</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="18"/>
+        <v>11.32654755966554</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="18"/>
+        <v>11.330433208561097</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="18"/>
+        <v>10.985030093669994</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="18"/>
+        <v>10.989128660788674</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
+        <v>10.992844989772889</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
@@ -4562,21 +4710,27 @@
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="19">+SUM(E36:E39)/E35</f>
+        <v>4.0069290167661148E-3</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="19"/>
+        <v>4.5031609759227428E-3</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="19"/>
+        <v>5.5021677113197042E-3</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="19"/>
+        <v>6.508219961418228E-3</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="19"/>
+        <v>7.5027060618517811E-3</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="19"/>
+        <v>8.9981109791381284E-3</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
@@ -4592,21 +4746,27 @@
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
+        <v>2825.7024980777151</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="20">+IFERROR(F51/SUM(F36:F39),0)</f>
+        <v>2515.2437632644514</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="20"/>
+        <v>2059.2671476099868</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="20"/>
+        <v>1687.8701332762284</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="20"/>
+        <v>1464.6886830158439</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="20"/>
+        <v>1221.6836417398606</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
@@ -4622,21 +4782,27 @@
       </c>
       <c r="E50" s="65">
         <f>+E36*$D$8+E38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="F50" s="65">
         <f t="shared" ref="F50:J50" si="21">+F36*$D$8+F38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="G50" s="65">
         <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="H50" s="65">
         <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="I50" s="65">
         <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="J50" s="65">
         <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
@@ -4648,27 +4814,35 @@
       <c r="B51" s="136"/>
       <c r="C51" s="110">
         <f>+C45</f>
+        <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
+        <v>215000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
+        <v>356038.51475779212</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="22">SUM(F45,F50)+F44</f>
+        <v>357164.61438355211</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="22"/>
+        <v>358312.4836841377</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="22"/>
+        <v>281874.31225713016</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="22"/>
+        <v>282684.91582205787</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
+        <v>283430.60488364764</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -4698,29 +4872,36 @@
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
+        <v>541880.83200000005</v>
       </c>
       <c r="E54" s="28">
         <f t="shared" ref="E54:J54" si="23">+E75*E76</f>
+        <v>311038.51475779212</v>
       </c>
       <c r="F54" s="28">
         <f t="shared" si="23"/>
+        <v>312164.61438355211</v>
       </c>
       <c r="G54" s="28">
         <f t="shared" si="23"/>
+        <v>313312.4836841377</v>
       </c>
       <c r="H54" s="28">
         <f t="shared" si="23"/>
+        <v>236874.31225713014</v>
       </c>
       <c r="I54" s="28">
         <f t="shared" si="23"/>
+        <v>237684.91582205784</v>
       </c>
       <c r="J54" s="28">
         <f t="shared" si="23"/>
+        <v>238430.60488364764</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
       <c r="N54" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
@@ -4731,24 +4912,31 @@
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
+        <v>215000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
+        <v>656038.51475779212</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="24">SUM(F65:F72)+F54</f>
+        <v>657164.61438355211</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="24"/>
+        <v>658312.4836841377</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="24"/>
+        <v>581874.31225713016</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="24"/>
+        <v>582684.91582205787</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="24"/>
+        <v>583430.60488364764</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
@@ -4764,21 +4952,27 @@
       </c>
       <c r="E56" s="28">
         <f>+SUM(E65:E67)/(E28-D28)</f>
+        <v>27.035307137850914</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" ref="F56:J56" si="25">+SUM(F65:F67)/(F28-E28)</f>
+        <v>27.035307137850914</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="25"/>
+        <v>26.870589591746796</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="25"/>
+        <v>26.70624976076785</v>
       </c>
       <c r="I56" s="28">
         <f t="shared" si="25"/>
+        <v>26.542294454493064</v>
       </c>
       <c r="J56" s="28">
         <f t="shared" si="25"/>
+        <v>26.378730412693315</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
@@ -4794,21 +4988,27 @@
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
+        <v>20.862696515072557</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="26">+F61/F35</f>
+        <v>20.840267931333308</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="26"/>
+        <v>20.816929262560585</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="26"/>
+        <v>22.676443198014116</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="26"/>
+        <v>22.651366062630821</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="26"/>
+        <v>22.628333324865295</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
@@ -4824,21 +5024,27 @@
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="27">+SUM(E36:E39)/E35</f>
+        <v>4.0069290167661148E-3</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="27"/>
+        <v>4.5031609759227428E-3</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="27"/>
+        <v>5.5021677113197042E-3</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="27"/>
+        <v>6.508219961418228E-3</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="27"/>
+        <v>7.5027060618517811E-3</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="27"/>
+        <v>8.9981109791381284E-3</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
@@ -4852,21 +5058,27 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
+        <v>5206.6548790300958</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="28">+IFERROR(F55/F40,0)</f>
+        <v>4627.9198196024799</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="28"/>
+        <v>3783.4050786444695</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="28"/>
+        <v>3484.2773189049713</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="28"/>
+        <v>3019.0928280935641</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="28"/>
+        <v>2514.7870900157227</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
@@ -4895,24 +5107,31 @@
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
+        <v>215000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
+        <v>656038.51475779212</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="29">+SUM(F65:F72)+F54</f>
+        <v>657164.61438355211</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="29"/>
+        <v>658312.4836841377</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="29"/>
+        <v>581874.31225713016</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="29"/>
+        <v>582684.91582205787</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="29"/>
+        <v>583430.60488364764</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -4963,7 +5182,7 @@
         <v>50</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C66" s="90">
         <v>0</v>
@@ -4990,41 +5209,39 @@
         <v>30000</v>
       </c>
       <c r="N66" s="69" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C67" s="90">
+        <v>0</v>
+      </c>
+      <c r="D67" s="51">
+        <v>0</v>
+      </c>
+      <c r="E67" s="51">
+        <v>0</v>
+      </c>
+      <c r="F67" s="51">
+        <v>0</v>
+      </c>
+      <c r="G67" s="51">
+        <v>0</v>
+      </c>
+      <c r="H67" s="51">
+        <v>0</v>
+      </c>
+      <c r="I67" s="51">
+        <v>0</v>
+      </c>
+      <c r="J67" s="51">
+        <v>0</v>
+      </c>
+      <c r="N67" s="69" t="s">
         <v>188</v>
-      </c>
-      <c r="C67" s="90">
-        <v>0</v>
-      </c>
-      <c r="D67" s="51">
-        <v>0</v>
-      </c>
-      <c r="E67" s="28">
-        <v>0</v>
-      </c>
-      <c r="F67" s="28">
-        <v>0</v>
-      </c>
-      <c r="G67" s="28">
-        <v>0</v>
-      </c>
-      <c r="H67" s="28">
-        <v>0</v>
-      </c>
-      <c r="I67" s="28">
-        <v>0</v>
-      </c>
-      <c r="J67" s="28">
-        <v>0</v>
-      </c>
-      <c r="N67" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サンクスLINE誘導：オプション（初期15万円・月3万円〜）</t>
-        </is>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5040,24 +5257,30 @@
       </c>
       <c r="E68" s="28">
         <f t="shared" ref="E68:J68" si="30">IF(E34&lt;5000,5000,15000)</f>
+        <v>15000</v>
       </c>
       <c r="F68" s="28">
         <f t="shared" si="30"/>
+        <v>15000</v>
       </c>
       <c r="G68" s="28">
         <f t="shared" si="30"/>
+        <v>15000</v>
       </c>
       <c r="H68" s="28">
         <f t="shared" si="30"/>
+        <v>15000</v>
       </c>
       <c r="I68" s="28">
         <f t="shared" si="30"/>
+        <v>15000</v>
       </c>
       <c r="J68" s="28">
         <f t="shared" si="30"/>
+        <v>15000</v>
       </c>
       <c r="N68" s="69" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O68" s="17" t="s">
         <v>131</v>
@@ -5069,7 +5292,7 @@
     <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="15"/>
       <c r="B69" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C69" s="90">
         <v>0</v>
@@ -5096,7 +5319,7 @@
         <v>300000</v>
       </c>
       <c r="N69" s="69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O69" s="5" t="s">
         <v>52</v>
@@ -5208,24 +5431,31 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
+        <v>215000</v>
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="31">SUM(E65:E72)+E54</f>
+        <v>656038.51475779212</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="31"/>
+        <v>657164.61438355211</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="31"/>
+        <v>658312.4836841377</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="31"/>
+        <v>581874.31225713016</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="31"/>
+        <v>582684.91582205787</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="31"/>
+        <v>583430.60488364764</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5246,24 +5476,31 @@
       </c>
       <c r="D75" s="41">
         <f t="shared" ref="D75:J75" si="32">+IF(D34&lt;30001,0,D34-30000)</f>
+        <v>180626.94400000002</v>
       </c>
       <c r="E75" s="41">
         <f t="shared" si="32"/>
+        <v>103679.50491926403</v>
       </c>
       <c r="F75" s="41">
         <f t="shared" si="32"/>
+        <v>104054.87146118403</v>
       </c>
       <c r="G75" s="41">
         <f t="shared" si="32"/>
+        <v>104437.49456137922</v>
       </c>
       <c r="H75" s="41">
         <f t="shared" si="32"/>
+        <v>78958.104085710045</v>
       </c>
       <c r="I75" s="41">
         <f t="shared" si="32"/>
+        <v>79228.30527401928</v>
       </c>
       <c r="J75" s="41">
         <f t="shared" si="32"/>
+        <v>79476.868294549218</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5272,24 +5509,31 @@
       </c>
       <c r="D76" s="5">
         <f t="shared" ref="D76:J76" si="33">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="F76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="G76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="H76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="J76" s="5">
         <f t="shared" si="33"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5379,14 +5623,17 @@
         <v>140</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="86">
+      <c r="C4" s="86" t="str">
         <f>+SIM①_月3投稿!D24</f>
+        <v>--</v>
       </c>
       <c r="D4" s="28">
         <f>+SIM①_月3投稿!G51</f>
+        <v>358312.4836841377</v>
       </c>
       <c r="E4" s="28">
         <f>+SIM①_月3投稿!J51</f>
+        <v>283430.60488364764</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -5395,14 +5642,17 @@
         <v>141</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="86">
+      <c r="C5" s="86" t="str">
         <f>+SIM①_月3投稿!D25</f>
+        <v>--</v>
       </c>
       <c r="D5" s="28">
         <f>+SIM①_月3投稿!G61</f>
+        <v>658312.4836841377</v>
       </c>
       <c r="E5" s="28">
         <f>+SIM①_月3投稿!J61</f>
+        <v>583430.60488364764</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -5413,12 +5663,15 @@
       <c r="B6" s="7"/>
       <c r="C6" s="117">
         <f>+SIM①_月3投稿!D28</f>
+        <v>79904</v>
       </c>
       <c r="D6" s="87">
         <f>+SIM①_月3投稿!G28</f>
+        <v>83239.782370400004</v>
       </c>
       <c r="E6" s="87">
         <f>+SIM①_月3投稿!J28</f>
+        <v>86630.666376967449</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -5429,12 +5682,15 @@
       <c r="B7" s="7"/>
       <c r="C7" s="88">
         <f>+SIM①_月3投稿!D27</f>
+        <v>0.34100000000000003</v>
       </c>
       <c r="D7" s="89">
         <f>+SIM①_月3投稿!G27</f>
+        <v>0.35499999999999998</v>
       </c>
       <c r="E7" s="89">
         <f>+SIM①_月3投稿!J27</f>
+        <v>0.376</v>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -5445,12 +5701,15 @@
       <c r="B8" s="7"/>
       <c r="C8" s="117">
         <f>+SIM①_月3投稿!D29</f>
+        <v>52656.736000000004</v>
       </c>
       <c r="D8" s="10">
         <f>+SIM①_月3投稿!G29</f>
+        <v>53689.659628908004</v>
       </c>
       <c r="E8" s="10">
         <f>+SIM①_月3投稿!J29</f>
+        <v>54057.535819227691</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -5469,12 +5728,15 @@
       <c r="B10" s="7"/>
       <c r="C10" s="117">
         <f>+SIM①_月3投稿!D34</f>
+        <v>210626.94400000002</v>
       </c>
       <c r="D10" s="10">
         <f>+SIM①_月3投稿!G34</f>
+        <v>134437.49456137922</v>
       </c>
       <c r="E10" s="10">
         <f>+SIM①_月3投稿!J34</f>
+        <v>109476.86829454922</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -5485,12 +5747,15 @@
       <c r="B11" s="7"/>
       <c r="C11" s="117">
         <f>+SIM①_月3投稿!D35</f>
+        <v>6165.8931586560011</v>
       </c>
       <c r="D11" s="10">
         <f>+SIM①_月3投稿!G35</f>
+        <v>31623.899729924047</v>
       </c>
       <c r="E11" s="10">
         <f>+SIM①_月3投稿!J35</f>
+        <v>25783.189442526949</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -5501,12 +5766,15 @@
       <c r="B12" s="7"/>
       <c r="C12" s="28">
         <f>+IFERROR(C5/C11,0)</f>
+        <v>0</v>
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
+        <v>11.330433208561097</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
+        <v>10.992844989772889</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -5517,12 +5785,15 @@
       <c r="B13" s="7"/>
       <c r="C13" s="28">
         <f>+IFERROR(C6/C12,0)</f>
+        <v>0</v>
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
+        <v>20.816929262560585</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
+        <v>22.628333324865295</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -5539,17 +5810,20 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="85" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="87">
         <f>+SIM①_月3投稿!D16</f>
+        <v>400</v>
       </c>
       <c r="D15" s="87">
         <f>+SIM①_月3投稿!G16</f>
+        <v>400</v>
       </c>
       <c r="E15" s="87">
         <f>+SIM①_月3投稿!J16</f>
+        <v>400</v>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -5558,17 +5832,20 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="85" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="87">
         <f>+C17</f>
+        <v>0</v>
       </c>
       <c r="D16" s="87">
         <f>+D17</f>
+        <v>174</v>
       </c>
       <c r="E16" s="87">
         <f>+E17</f>
+        <v>232</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -5583,17 +5860,20 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="85" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
         <f>+SIM①_月3投稿!D36</f>
+        <v>0</v>
       </c>
       <c r="D17" s="87">
         <f>+SIM①_月3投稿!G36</f>
+        <v>174</v>
       </c>
       <c r="E17" s="87">
         <f>+SIM①_月3投稿!J36</f>
+        <v>232</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -5625,12 +5905,15 @@
       <c r="B18" s="7"/>
       <c r="C18" s="87">
         <f>+SIM①_月3投稿!D37</f>
+        <v>0</v>
       </c>
       <c r="D18" s="87">
         <f>+SIM①_月3投稿!G37</f>
+        <v>0</v>
       </c>
       <c r="E18" s="87">
         <f>+SIM①_月3投稿!J37</f>
+        <v>0</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -5650,6 +5933,7 @@
       </c>
       <c r="X18" s="34">
         <f>+T18*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Y18" s="35">
         <v>2.5</v>
@@ -5662,12 +5946,15 @@
       <c r="B19" s="7"/>
       <c r="C19" s="87">
         <f>+SIM①_月3投稿!D38</f>
+        <v>0</v>
       </c>
       <c r="D19" s="87">
         <f>+SIM①_月3投稿!G38</f>
+        <v>0</v>
       </c>
       <c r="E19" s="87">
         <f>+SIM①_月3投稿!J38</f>
+        <v>0</v>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -5683,12 +5970,15 @@
       <c r="B20" s="7"/>
       <c r="C20" s="87">
         <f>+SIM①_月3投稿!D39</f>
+        <v>0</v>
       </c>
       <c r="D20" s="87">
         <f>+SIM①_月3投稿!G39</f>
+        <v>0</v>
       </c>
       <c r="E20" s="87">
         <f>+SIM①_月3投稿!J39</f>
+        <v>0</v>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -5715,14 +6005,17 @@
         <v>142</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="90">
+      <c r="C22" s="90" t="str">
         <f>+IFERROR(C4/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
+        <v>2059.2671476099868</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
+        <v>1221.6836417398606</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -5736,14 +6029,17 @@
         <v>143</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="90">
+      <c r="C23" s="90" t="str">
         <f>+IFERROR(C5/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
+        <v>3783.4050786444695</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
+        <v>2514.7870900157227</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -5772,12 +6068,15 @@
       <c r="B25" s="7"/>
       <c r="C25" s="10">
         <f>+SIM①_月3投稿!E68+C29*C30</f>
+        <v>556880.83200000005</v>
       </c>
       <c r="D25" s="10">
         <f>+SIM①_月3投稿!G68+D29*D30</f>
+        <v>328312.4836841377</v>
       </c>
       <c r="E25" s="10">
         <f>+SIM①_月3投稿!J68+E29*E30</f>
+        <v>253430.60488364764</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -5813,12 +6112,15 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
+        <v>180626.94400000002</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
+        <v>104437.49456137922</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
+        <v>79476.868294549218</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -5833,12 +6135,15 @@
       </c>
       <c r="C30" s="5">
         <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E30" s="5">
         <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="R30" s="34"/>
       <c r="T30" s="34"/>
@@ -5908,7 +6213,7 @@
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="56" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -5979,7 +6284,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D8" s="33">
         <v>0</v>
@@ -5998,7 +6303,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="69" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O8" s="35" t="s">
         <v>158</v>
@@ -6048,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H10" s="125">
         <v>400</v>
@@ -6059,7 +6364,7 @@
       <c r="J10" s="29"/>
       <c r="K10" s="118"/>
       <c r="N10" s="132" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
@@ -6106,22 +6411,22 @@
         <v>29</v>
       </c>
       <c r="E13" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="G13" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="G13" s="36" t="s">
+      <c r="H13" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="H13" s="36" t="s">
+      <c r="I13" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="I13" s="36" t="s">
+      <c r="J13" s="36" t="s">
         <v>172</v>
-      </c>
-      <c r="J13" s="36" t="s">
-        <v>173</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>1</v>
@@ -6218,7 +6523,7 @@
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
       <c r="N15" s="69" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O15" s="17" t="s">
         <v>33</v>
@@ -6358,7 +6663,7 @@
         <v>22</v>
       </c>
       <c r="N18" s="69" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O18" s="22" t="s">
         <v>39</v>
@@ -6559,7 +6864,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="7"/>
       <c r="N22" s="69" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O22" s="17" t="s">
         <v>41</v>
@@ -6662,7 +6967,7 @@
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
       <c r="N24" s="69" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O24" s="22" t="s">
         <v>44</v>
@@ -6763,7 +7068,7 @@
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
       <c r="N26" s="72" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O26" s="17" t="s">
         <v>41</v>
@@ -6812,7 +7117,7 @@
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
       <c r="N27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O27" s="17" t="s">
         <v>42</v>
@@ -6865,7 +7170,7 @@
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
       <c r="N28" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O28" s="22" t="s">
         <v>44</v>
@@ -6957,7 +7262,7 @@
       <c r="K30" s="11"/>
       <c r="L30" s="7"/>
       <c r="N30" s="69" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O30" s="17" t="s">
         <v>122</v>
@@ -7041,7 +7346,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
       <c r="N32" s="69" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O32" s="17" t="s">
         <v>126</v>
@@ -7240,7 +7545,7 @@
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O36" s="17" t="s">
         <v>127</v>
@@ -7544,7 +7849,7 @@
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
       <c r="N45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -7821,7 +8126,7 @@
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
       <c r="N54" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
@@ -8102,7 +8407,7 @@
         <v>50</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C66" s="90">
         <v>0</v>
@@ -8129,12 +8434,12 @@
         <v>30000</v>
       </c>
       <c r="N66" s="69" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C67" s="90">
         <v>0</v>
@@ -8161,7 +8466,7 @@
         <v>0</v>
       </c>
       <c r="N67" s="69" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8200,7 +8505,7 @@
         <v>15000</v>
       </c>
       <c r="N68" s="69" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O68" s="17" t="s">
         <v>131</v>
@@ -8212,7 +8517,7 @@
     <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="15"/>
       <c r="B69" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C69" s="90">
         <v>0</v>
@@ -8239,7 +8544,7 @@
         <v>350000</v>
       </c>
       <c r="N69" s="69" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O69" s="5" t="s">
         <v>52</v>
@@ -8730,7 +9035,7 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="85" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="87">
@@ -8752,7 +9057,7 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="85" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="87">
@@ -8780,7 +9085,7 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="85" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
